--- a/stock.xlsx
+++ b/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86155\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF70DE-EF17-49D0-9F2C-D911B4C9457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5091CD-B5E8-49BF-A798-C1ECFCCD7F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6386" uniqueCount="3199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6387" uniqueCount="3200">
   <si>
     <t>编码</t>
   </si>
@@ -9653,6 +9653,10 @@
   </si>
   <si>
     <t>4.81</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -9845,17 +9849,17 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10140,17 +10144,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>3194</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
@@ -10174,7 +10178,9 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="7" t="s">
+        <v>3199</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
@@ -10201,7 +10207,7 @@
       <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9" t="s">
         <v>3195</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -10230,7 +10236,7 @@
       <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>3195</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -10259,7 +10265,7 @@
       <c r="G5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>3196</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -10288,7 +10294,7 @@
       <c r="G6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>3196</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -10315,7 +10321,7 @@
       <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9" t="s">
         <v>3197</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -10344,7 +10350,7 @@
       <c r="G8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="9" t="s">
         <v>3198</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -10373,7 +10379,7 @@
       <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>3198</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -10402,7 +10408,7 @@
       <c r="G10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>59.71</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -10431,7 +10437,7 @@
       <c r="G11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>59.71</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -10460,7 +10466,7 @@
       <c r="G12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>7.11</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -10489,7 +10495,7 @@
       <c r="G13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>7.11</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -10518,7 +10524,7 @@
       <c r="G14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>5.58</v>
       </c>
       <c r="I14" s="6" t="s">
@@ -10545,7 +10551,7 @@
       <c r="G15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>3.75</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -10572,7 +10578,7 @@
       <c r="G16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <v>3.75</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -10599,7 +10605,7 @@
       <c r="G17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>0.54</v>
       </c>
       <c r="I17" s="6" t="s">
@@ -10626,7 +10632,7 @@
       <c r="G18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>0.54</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -10655,7 +10661,7 @@
       <c r="G19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>46.2</v>
       </c>
       <c r="I19" s="6" t="s">
@@ -10684,7 +10690,7 @@
       <c r="G20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>130</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -10713,7 +10719,7 @@
       <c r="G21" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>67.38</v>
       </c>
       <c r="I21" s="6" t="s">
@@ -10742,7 +10748,7 @@
       <c r="G22" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>6.66</v>
       </c>
       <c r="I22" s="6" t="s">
@@ -10771,7 +10777,7 @@
       <c r="G23" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>6.66</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -10800,7 +10806,7 @@
       <c r="G24" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>13.32</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -10829,7 +10835,7 @@
       <c r="G25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>13.32</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -10856,7 +10862,7 @@
       <c r="G26" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>4.6900000000000004</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -10883,7 +10889,7 @@
       <c r="G27" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>4.6900000000000004</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -10910,7 +10916,7 @@
       <c r="G28" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>5.73</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -10937,7 +10943,7 @@
       <c r="G29" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>5.73</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -10964,7 +10970,7 @@
       <c r="G30" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <v>9.75</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -10991,7 +10997,7 @@
       <c r="G31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>6.58</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -11018,7 +11024,7 @@
       <c r="G32" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <v>4.17</v>
       </c>
       <c r="I32" s="6" t="s">
@@ -11047,7 +11053,7 @@
       <c r="G33" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>27.33</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -11074,7 +11080,7 @@
       <c r="G34" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="8">
         <v>4.6399999999999997</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -11103,7 +11109,7 @@
       <c r="G35" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="8">
         <v>79.599999999999994</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -11132,7 +11138,7 @@
       <c r="G36" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="8">
         <v>13.88</v>
       </c>
       <c r="I36" s="6" t="s">
@@ -11161,7 +11167,7 @@
       <c r="G37" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="8">
         <v>13.88</v>
       </c>
       <c r="I37" s="6" t="s">
@@ -11188,7 +11194,7 @@
       <c r="G38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="8">
         <v>44.2</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -11217,7 +11223,7 @@
       <c r="G39" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="8">
         <v>479</v>
       </c>
       <c r="I39" s="6" t="s">
@@ -11244,7 +11250,7 @@
       <c r="G40" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="8">
         <v>7.66</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -11271,7 +11277,7 @@
       <c r="G41" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="8">
         <v>7.66</v>
       </c>
       <c r="I41" s="6" t="s">
@@ -11300,7 +11306,7 @@
       <c r="G42" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="8">
         <v>30.58</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -11327,7 +11333,7 @@
       <c r="G43" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="8">
         <v>6.9</v>
       </c>
       <c r="I43" s="6" t="s">
@@ -11356,7 +11362,7 @@
       <c r="G44" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="8">
         <v>4.7</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -11383,7 +11389,7 @@
       <c r="G45" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="8">
         <v>17.260000000000002</v>
       </c>
       <c r="I45" s="6" t="s">
@@ -11412,7 +11418,7 @@
       <c r="G46" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="8">
         <v>60.42</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -11439,7 +11445,7 @@
       <c r="G47" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="8">
         <v>35.99</v>
       </c>
       <c r="I47" s="6" t="s">
@@ -11466,7 +11472,7 @@
       <c r="G48" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="8">
         <v>23.77</v>
       </c>
       <c r="I48" s="6" t="s">
@@ -11493,7 +11499,7 @@
       <c r="G49" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="8">
         <v>23.77</v>
       </c>
       <c r="I49" s="6" t="s">
@@ -11520,7 +11526,7 @@
       <c r="G50" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="8">
         <v>285.24</v>
       </c>
       <c r="I50" s="6" t="s">
@@ -11547,7 +11553,7 @@
       <c r="G51" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="8">
         <v>8.08</v>
       </c>
       <c r="I51" s="6" t="s">
@@ -11574,7 +11580,7 @@
       <c r="G52" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="8">
         <v>8.08</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -11601,7 +11607,7 @@
       <c r="G53" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="8">
         <v>17.8</v>
       </c>
       <c r="I53" s="6" t="s">
@@ -11630,7 +11636,7 @@
       <c r="G54" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="8">
         <v>96.45</v>
       </c>
       <c r="I54" s="6" t="s">
@@ -11657,7 +11663,7 @@
       <c r="G55" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="8">
         <v>26.7</v>
       </c>
       <c r="I55" s="6" t="s">
@@ -11686,7 +11692,7 @@
       <c r="G56" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="8">
         <v>238.27</v>
       </c>
       <c r="I56" s="6" t="s">
@@ -11715,7 +11721,7 @@
       <c r="G57" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="8">
         <v>317.39</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -11744,7 +11750,7 @@
       <c r="G58" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="8">
         <v>46.6</v>
       </c>
       <c r="I58" s="6" t="s">
@@ -11773,7 +11779,7 @@
       <c r="G59" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="8">
         <v>94.75</v>
       </c>
       <c r="I59" s="6" t="s">
@@ -11802,7 +11808,7 @@
       <c r="G60" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="8">
         <v>94.75</v>
       </c>
       <c r="I60" s="6" t="s">
@@ -11831,7 +11837,7 @@
       <c r="G61" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="8">
         <v>69.459999999999994</v>
       </c>
       <c r="I61" s="6" t="s">
@@ -11860,7 +11866,7 @@
       <c r="G62" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="8">
         <v>105</v>
       </c>
       <c r="I62" s="6" t="s">
@@ -11889,7 +11895,7 @@
       <c r="G63" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="8">
         <v>3.81</v>
       </c>
       <c r="I63" s="6" t="s">
@@ -11918,7 +11924,7 @@
       <c r="G64" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="8">
         <v>3.81</v>
       </c>
       <c r="I64" s="6" t="s">
@@ -11947,7 +11953,7 @@
       <c r="G65" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="8">
         <v>21.6</v>
       </c>
       <c r="I65" s="6" t="s">
@@ -11974,7 +11980,7 @@
       <c r="G66" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="8">
         <v>7.35</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -12001,7 +12007,7 @@
       <c r="G67" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H67" s="10">
+      <c r="H67" s="8">
         <v>7.35</v>
       </c>
       <c r="I67" s="6" t="s">
@@ -12028,7 +12034,7 @@
       <c r="G68" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="8">
         <v>6.4</v>
       </c>
       <c r="I68" s="6" t="s">
@@ -12055,7 +12061,7 @@
       <c r="G69" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="8">
         <v>6.4</v>
       </c>
       <c r="I69" s="6" t="s">
@@ -12082,7 +12088,7 @@
       <c r="G70" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="8">
         <v>9.9600000000000009</v>
       </c>
       <c r="I70" s="6" t="s">
@@ -12109,7 +12115,7 @@
       <c r="G71" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H71" s="10">
+      <c r="H71" s="8">
         <v>9.9600000000000009</v>
       </c>
       <c r="I71" s="6" t="s">
@@ -12136,7 +12142,7 @@
       <c r="G72" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="8">
         <v>97.16</v>
       </c>
       <c r="I72" s="6" t="s">
@@ -12163,7 +12169,7 @@
       <c r="G73" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H73" s="10">
+      <c r="H73" s="8">
         <v>97.16</v>
       </c>
       <c r="I73" s="6" t="s">
@@ -12192,7 +12198,7 @@
       <c r="G74" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="8">
         <v>19.97</v>
       </c>
       <c r="I74" s="6" t="s">
@@ -12221,7 +12227,7 @@
       <c r="G75" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="8">
         <v>19.97</v>
       </c>
       <c r="I75" s="6" t="s">
@@ -12248,7 +12254,7 @@
       <c r="G76" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="8">
         <v>6.58</v>
       </c>
       <c r="I76" s="6" t="s">
@@ -12275,7 +12281,7 @@
       <c r="G77" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="8">
         <v>6.58</v>
       </c>
       <c r="I77" s="6" t="s">
@@ -12302,7 +12308,7 @@
       <c r="G78" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="8">
         <v>18.95</v>
       </c>
       <c r="I78" s="6" t="s">
@@ -12329,7 +12335,7 @@
       <c r="G79" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="8">
         <v>18.95</v>
       </c>
       <c r="I79" s="6" t="s">
@@ -12358,7 +12364,7 @@
       <c r="G80" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="8">
         <v>13.51</v>
       </c>
       <c r="I80" s="6" t="s">
@@ -12385,7 +12391,7 @@
       <c r="G81" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="8">
         <v>17.8</v>
       </c>
       <c r="I81" s="6" t="s">
@@ -12414,7 +12420,7 @@
       <c r="G82" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="8">
         <v>76.569999999999993</v>
       </c>
       <c r="I82" s="6" t="s">
@@ -12441,7 +12447,7 @@
       <c r="G83" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="8">
         <v>18.45</v>
       </c>
       <c r="I83" s="6" t="s">
@@ -12468,7 +12474,7 @@
       <c r="G84" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="H84" s="10">
+      <c r="H84" s="8">
         <v>18.45</v>
       </c>
       <c r="I84" s="6" t="s">
@@ -12495,7 +12501,7 @@
       <c r="G85" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85" s="8">
         <v>22.49</v>
       </c>
       <c r="I85" s="6" t="s">
@@ -12522,7 +12528,7 @@
       <c r="G86" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="8">
         <v>6.09</v>
       </c>
       <c r="I86" s="6" t="s">
@@ -12549,7 +12555,7 @@
       <c r="G87" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="8">
         <v>6.09</v>
       </c>
       <c r="I87" s="6" t="s">
@@ -12576,7 +12582,7 @@
       <c r="G88" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="8">
         <v>32.159999999999997</v>
       </c>
       <c r="I88" s="6" t="s">
@@ -12603,7 +12609,7 @@
       <c r="G89" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="8">
         <v>32.159999999999997</v>
       </c>
       <c r="I89" s="6" t="s">
@@ -12632,7 +12638,7 @@
       <c r="G90" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="8">
         <v>17.43</v>
       </c>
       <c r="I90" s="6" t="s">
@@ -12661,7 +12667,7 @@
       <c r="G91" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="8">
         <v>17.43</v>
       </c>
       <c r="I91" s="6" t="s">
@@ -12690,7 +12696,7 @@
       <c r="G92" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="8">
         <v>72.489999999999995</v>
       </c>
       <c r="I92" s="6" t="s">
@@ -12719,7 +12725,7 @@
       <c r="G93" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="8">
         <v>72.489999999999995</v>
       </c>
       <c r="I93" s="6" t="s">
@@ -12748,7 +12754,7 @@
       <c r="G94" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="8">
         <v>20.2</v>
       </c>
       <c r="I94" s="6" t="s">
@@ -12777,7 +12783,7 @@
       <c r="G95" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="8">
         <v>20.2</v>
       </c>
       <c r="I95" s="6" t="s">
@@ -12806,7 +12812,7 @@
       <c r="G96" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="8">
         <v>29.01</v>
       </c>
       <c r="I96" s="6" t="s">
@@ -12833,7 +12839,7 @@
       <c r="G97" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="8">
         <v>16.46</v>
       </c>
       <c r="I97" s="6" t="s">
@@ -12860,7 +12866,7 @@
       <c r="G98" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="8">
         <v>16.46</v>
       </c>
       <c r="I98" s="6" t="s">
@@ -12887,7 +12893,7 @@
       <c r="G99" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="H99" s="10">
+      <c r="H99" s="8">
         <v>16.579999999999998</v>
       </c>
       <c r="I99" s="6" t="s">
@@ -12914,7 +12920,7 @@
       <c r="G100" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="8">
         <v>16.579999999999998</v>
       </c>
       <c r="I100" s="6" t="s">
@@ -12943,7 +12949,7 @@
       <c r="G101" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="8">
         <v>68</v>
       </c>
       <c r="I101" s="6" t="s">
@@ -12972,7 +12978,7 @@
       <c r="G102" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="8">
         <v>68</v>
       </c>
       <c r="I102" s="6" t="s">
@@ -12999,7 +13005,7 @@
       <c r="G103" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="H103" s="10">
+      <c r="H103" s="8">
         <v>15.48</v>
       </c>
       <c r="I103" s="6" t="s">
@@ -13026,7 +13032,7 @@
       <c r="G104" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="8">
         <v>15.48</v>
       </c>
       <c r="I104" s="6" t="s">
@@ -13053,7 +13059,7 @@
       <c r="G105" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="8">
         <v>320.99</v>
       </c>
       <c r="I105" s="6" t="s">
@@ -13080,7 +13086,7 @@
       <c r="G106" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="H106" s="10">
+      <c r="H106" s="8">
         <v>320.99</v>
       </c>
       <c r="I106" s="6" t="s">
@@ -13107,7 +13113,7 @@
       <c r="G107" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="H107" s="10">
+      <c r="H107" s="8">
         <v>214.43</v>
       </c>
       <c r="I107" s="6" t="s">
@@ -13134,7 +13140,7 @@
       <c r="G108" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="8">
         <v>214.43</v>
       </c>
       <c r="I108" s="6" t="s">
@@ -13161,7 +13167,7 @@
       <c r="G109" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="8">
         <v>11.4</v>
       </c>
       <c r="I109" s="6" t="s">
@@ -13188,7 +13194,7 @@
       <c r="G110" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="H110" s="10">
+      <c r="H110" s="8">
         <v>11.4</v>
       </c>
       <c r="I110" s="6" t="s">
@@ -13217,7 +13223,7 @@
       <c r="G111" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="H111" s="10">
+      <c r="H111" s="8">
         <v>91.34</v>
       </c>
       <c r="I111" s="6" t="s">
@@ -13246,7 +13252,7 @@
       <c r="G112" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H112" s="10">
+      <c r="H112" s="8">
         <v>87.98</v>
       </c>
       <c r="I112" s="6" t="s">
@@ -13273,7 +13279,7 @@
       <c r="G113" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="H113" s="10">
+      <c r="H113" s="8">
         <v>4.18</v>
       </c>
       <c r="I113" s="6" t="s">
@@ -13300,7 +13306,7 @@
       <c r="G114" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="H114" s="10">
+      <c r="H114" s="8">
         <v>4.18</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -13329,7 +13335,7 @@
       <c r="G115" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="H115" s="10">
+      <c r="H115" s="8">
         <v>7.98</v>
       </c>
       <c r="I115" s="6" t="s">
@@ -13358,7 +13364,7 @@
       <c r="G116" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="H116" s="10">
+      <c r="H116" s="8">
         <v>7.98</v>
       </c>
       <c r="I116" s="6" t="s">
@@ -13385,7 +13391,7 @@
       <c r="G117" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="H117" s="10">
+      <c r="H117" s="8">
         <v>73.02</v>
       </c>
       <c r="I117" s="6" t="s">
@@ -13412,7 +13418,7 @@
       <c r="G118" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="H118" s="10">
+      <c r="H118" s="8">
         <v>73.02</v>
       </c>
       <c r="I118" s="6" t="s">
@@ -13441,7 +13447,7 @@
       <c r="G119" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H119" s="10">
+      <c r="H119" s="8">
         <v>36.020000000000003</v>
       </c>
       <c r="I119" s="6" t="s">
@@ -13470,7 +13476,7 @@
       <c r="G120" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H120" s="10">
+      <c r="H120" s="8">
         <v>36.020000000000003</v>
       </c>
       <c r="I120" s="6" t="s">
@@ -13497,7 +13503,7 @@
       <c r="G121" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="8">
         <v>4.4400000000000004</v>
       </c>
       <c r="I121" s="6" t="s">
@@ -13526,7 +13532,7 @@
       <c r="G122" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H122" s="10">
+      <c r="H122" s="8">
         <v>27.89</v>
       </c>
       <c r="I122" s="6" t="s">
@@ -13555,7 +13561,7 @@
       <c r="G123" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H123" s="8">
         <v>27.89</v>
       </c>
       <c r="I123" s="6" t="s">
@@ -13584,7 +13590,7 @@
       <c r="G124" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="H124" s="10">
+      <c r="H124" s="8">
         <v>46.25</v>
       </c>
       <c r="I124" s="6" t="s">
@@ -13613,7 +13619,7 @@
       <c r="G125" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="H125" s="10">
+      <c r="H125" s="8">
         <v>46.25</v>
       </c>
       <c r="I125" s="6" t="s">
@@ -13640,7 +13646,7 @@
       <c r="G126" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="H126" s="10">
+      <c r="H126" s="8">
         <v>23.33</v>
       </c>
       <c r="I126" s="6" t="s">
@@ -13667,7 +13673,7 @@
       <c r="G127" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="H127" s="10">
+      <c r="H127" s="8">
         <v>23.33</v>
       </c>
       <c r="I127" s="6" t="s">
@@ -13694,7 +13700,7 @@
       <c r="G128" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="H128" s="10">
+      <c r="H128" s="8">
         <v>19.32</v>
       </c>
       <c r="I128" s="6" t="s">
@@ -13723,7 +13729,7 @@
       <c r="G129" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="H129" s="10">
+      <c r="H129" s="8">
         <v>155.68</v>
       </c>
       <c r="I129" s="6" t="s">
@@ -13752,7 +13758,7 @@
       <c r="G130" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="H130" s="10">
+      <c r="H130" s="8">
         <v>155.68</v>
       </c>
       <c r="I130" s="6" t="s">
@@ -13781,7 +13787,7 @@
       <c r="G131" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H131" s="10">
+      <c r="H131" s="8">
         <v>17.04</v>
       </c>
       <c r="I131" s="6" t="s">
@@ -13810,7 +13816,7 @@
       <c r="G132" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H132" s="10">
+      <c r="H132" s="8">
         <v>17.04</v>
       </c>
       <c r="I132" s="6" t="s">
@@ -13837,7 +13843,7 @@
       <c r="G133" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="H133" s="10">
+      <c r="H133" s="8">
         <v>35.200000000000003</v>
       </c>
       <c r="I133" s="6" t="s">
@@ -13864,7 +13870,7 @@
       <c r="G134" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="H134" s="10">
+      <c r="H134" s="8">
         <v>35.200000000000003</v>
       </c>
       <c r="I134" s="6" t="s">
@@ -13891,7 +13897,7 @@
       <c r="G135" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="H135" s="10">
+      <c r="H135" s="8">
         <v>13</v>
       </c>
       <c r="I135" s="6" t="s">
@@ -13918,7 +13924,7 @@
       <c r="G136" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="H136" s="10">
+      <c r="H136" s="8">
         <v>1.88</v>
       </c>
       <c r="I136" s="6" t="s">
@@ -13945,7 +13951,7 @@
       <c r="G137" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="H137" s="10">
+      <c r="H137" s="8">
         <v>1.88</v>
       </c>
       <c r="I137" s="6" t="s">
@@ -13972,7 +13978,7 @@
       <c r="G138" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H138" s="10">
+      <c r="H138" s="8">
         <v>5.75</v>
       </c>
       <c r="I138" s="6" t="s">
@@ -13999,7 +14005,7 @@
       <c r="G139" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H139" s="10">
+      <c r="H139" s="8">
         <v>5.75</v>
       </c>
       <c r="I139" s="6" t="s">
@@ -14026,7 +14032,7 @@
       <c r="G140" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="H140" s="10">
+      <c r="H140" s="8">
         <v>25.62</v>
       </c>
       <c r="I140" s="6" t="s">
@@ -14055,7 +14061,7 @@
       <c r="G141" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="H141" s="10">
+      <c r="H141" s="8">
         <v>37.56</v>
       </c>
       <c r="I141" s="6" t="s">
@@ -14084,7 +14090,7 @@
       <c r="G142" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="H142" s="10">
+      <c r="H142" s="8">
         <v>37.56</v>
       </c>
       <c r="I142" s="6" t="s">
@@ -14111,7 +14117,7 @@
       <c r="G143" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="H143" s="10">
+      <c r="H143" s="8">
         <v>1.6</v>
       </c>
       <c r="I143" s="6" t="s">
@@ -14140,7 +14146,7 @@
       <c r="G144" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H144" s="10">
+      <c r="H144" s="8">
         <v>21.61</v>
       </c>
       <c r="I144" s="6" t="s">
@@ -14169,7 +14175,7 @@
       <c r="G145" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H145" s="10">
+      <c r="H145" s="8">
         <v>21.61</v>
       </c>
       <c r="I145" s="6" t="s">
@@ -14198,7 +14204,7 @@
       <c r="G146" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H146" s="10">
+      <c r="H146" s="8">
         <v>1.63</v>
       </c>
       <c r="I146" s="6" t="s">
@@ -14227,7 +14233,7 @@
       <c r="G147" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H147" s="10">
+      <c r="H147" s="8">
         <v>1.63</v>
       </c>
       <c r="I147" s="6" t="s">
@@ -14256,7 +14262,7 @@
       <c r="G148" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H148" s="10">
+      <c r="H148" s="8">
         <v>23.07</v>
       </c>
       <c r="I148" s="6" t="s">
@@ -14285,7 +14291,7 @@
       <c r="G149" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="H149" s="10">
+      <c r="H149" s="8">
         <v>11.75</v>
       </c>
       <c r="I149" s="6" t="s">
@@ -14314,7 +14320,7 @@
       <c r="G150" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="H150" s="10">
+      <c r="H150" s="8">
         <v>11.75</v>
       </c>
       <c r="I150" s="6" t="s">
@@ -14341,7 +14347,7 @@
       <c r="G151" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="H151" s="10">
+      <c r="H151" s="8">
         <v>7.68</v>
       </c>
       <c r="I151" s="6" t="s">
@@ -14368,7 +14374,7 @@
       <c r="G152" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="H152" s="10">
+      <c r="H152" s="8">
         <v>7.68</v>
       </c>
       <c r="I152" s="6" t="s">
@@ -14397,7 +14403,7 @@
       <c r="G153" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="H153" s="10">
+      <c r="H153" s="8">
         <v>30.28</v>
       </c>
       <c r="I153" s="6" t="s">
@@ -14426,7 +14432,7 @@
       <c r="G154" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="H154" s="10">
+      <c r="H154" s="8">
         <v>30.28</v>
       </c>
       <c r="I154" s="6" t="s">
@@ -14453,7 +14459,7 @@
       <c r="G155" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="H155" s="10">
+      <c r="H155" s="8">
         <v>5.55</v>
       </c>
       <c r="I155" s="6" t="s">
@@ -14482,7 +14488,7 @@
       <c r="G156" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H156" s="10">
+      <c r="H156" s="8">
         <v>41.5</v>
       </c>
       <c r="I156" s="6" t="s">
@@ -14511,7 +14517,7 @@
       <c r="G157" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H157" s="10">
+      <c r="H157" s="8">
         <v>41.5</v>
       </c>
       <c r="I157" s="6" t="s">
@@ -14538,7 +14544,7 @@
       <c r="G158" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="H158" s="10">
+      <c r="H158" s="8">
         <v>15.4</v>
       </c>
       <c r="I158" s="6" t="s">
@@ -14565,7 +14571,7 @@
       <c r="G159" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="H159" s="10">
+      <c r="H159" s="8">
         <v>15.4</v>
       </c>
       <c r="I159" s="6" t="s">
@@ -14594,7 +14600,7 @@
       <c r="G160" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="H160" s="10">
+      <c r="H160" s="8">
         <v>22.7</v>
       </c>
       <c r="I160" s="6" t="s">
@@ -14623,7 +14629,7 @@
       <c r="G161" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="H161" s="10">
+      <c r="H161" s="8">
         <v>28.5</v>
       </c>
       <c r="I161" s="6" t="s">
@@ -14650,7 +14656,7 @@
       <c r="G162" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="H162" s="10">
+      <c r="H162" s="8">
         <v>6.2</v>
       </c>
       <c r="I162" s="6" t="s">
@@ -14677,7 +14683,7 @@
       <c r="G163" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="H163" s="10">
+      <c r="H163" s="8">
         <v>6.2</v>
       </c>
       <c r="I163" s="6" t="s">
@@ -14706,7 +14712,7 @@
       <c r="G164" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H164" s="10">
+      <c r="H164" s="8">
         <v>13.46</v>
       </c>
       <c r="I164" s="6" t="s">
@@ -14735,7 +14741,7 @@
       <c r="G165" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H165" s="10">
+      <c r="H165" s="8">
         <v>13.46</v>
       </c>
       <c r="I165" s="6" t="s">
@@ -14764,7 +14770,7 @@
       <c r="G166" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="H166" s="10">
+      <c r="H166" s="8">
         <v>12.1</v>
       </c>
       <c r="I166" s="6" t="s">
@@ -14793,7 +14799,7 @@
       <c r="G167" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="H167" s="10">
+      <c r="H167" s="8">
         <v>12.1</v>
       </c>
       <c r="I167" s="6" t="s">
@@ -14820,7 +14826,7 @@
       <c r="G168" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H168" s="10">
+      <c r="H168" s="8">
         <v>6.05</v>
       </c>
       <c r="I168" s="6" t="s">
@@ -14849,7 +14855,7 @@
       <c r="G169" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="H169" s="10">
+      <c r="H169" s="8">
         <v>2.0699999999999998</v>
       </c>
       <c r="I169" s="6" t="s">
@@ -14878,7 +14884,7 @@
       <c r="G170" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="H170" s="10">
+      <c r="H170" s="8">
         <v>2.0699999999999998</v>
       </c>
       <c r="I170" s="6" t="s">
@@ -14907,7 +14913,7 @@
       <c r="G171" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="H171" s="10">
+      <c r="H171" s="8">
         <v>31.99</v>
       </c>
       <c r="I171" s="6" t="s">
@@ -14936,7 +14942,7 @@
       <c r="G172" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="H172" s="10">
+      <c r="H172" s="8">
         <v>31.99</v>
       </c>
       <c r="I172" s="6" t="s">
@@ -14963,7 +14969,7 @@
       <c r="G173" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="H173" s="10">
+      <c r="H173" s="8">
         <v>3.91</v>
       </c>
       <c r="I173" s="6" t="s">
@@ -14990,7 +14996,7 @@
       <c r="G174" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="H174" s="10">
+      <c r="H174" s="8">
         <v>2.19</v>
       </c>
       <c r="I174" s="6" t="s">
@@ -15019,7 +15025,7 @@
       <c r="G175" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="H175" s="10">
+      <c r="H175" s="8">
         <v>11.58</v>
       </c>
       <c r="I175" s="6" t="s">
@@ -15046,7 +15052,7 @@
       <c r="G176" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="H176" s="10">
+      <c r="H176" s="8">
         <v>21.07</v>
       </c>
       <c r="I176" s="6" t="s">
@@ -15075,7 +15081,7 @@
       <c r="G177" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="H177" s="10">
+      <c r="H177" s="8">
         <v>19.3</v>
       </c>
       <c r="I177" s="6" t="s">
@@ -15104,7 +15110,7 @@
       <c r="G178" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="H178" s="10">
+      <c r="H178" s="8">
         <v>19.3</v>
       </c>
       <c r="I178" s="6" t="s">
@@ -15131,7 +15137,7 @@
       <c r="G179" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="H179" s="10">
+      <c r="H179" s="8">
         <v>7.78</v>
       </c>
       <c r="I179" s="6" t="s">
@@ -15160,7 +15166,7 @@
       <c r="G180" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="H180" s="10">
+      <c r="H180" s="8">
         <v>44.1</v>
       </c>
       <c r="I180" s="6" t="s">
@@ -15187,7 +15193,7 @@
       <c r="G181" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="H181" s="10">
+      <c r="H181" s="8">
         <v>25.14</v>
       </c>
       <c r="I181" s="6" t="s">
@@ -15214,7 +15220,7 @@
       <c r="G182" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="H182" s="10">
+      <c r="H182" s="8">
         <v>25.14</v>
       </c>
       <c r="I182" s="6" t="s">
@@ -15243,7 +15249,7 @@
       <c r="G183" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H183" s="10">
+      <c r="H183" s="8">
         <v>1.99</v>
       </c>
       <c r="I183" s="6" t="s">
@@ -15272,7 +15278,7 @@
       <c r="G184" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H184" s="10">
+      <c r="H184" s="8">
         <v>1.99</v>
       </c>
       <c r="I184" s="6" t="s">
@@ -15299,7 +15305,7 @@
       <c r="G185" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="H185" s="10">
+      <c r="H185" s="8">
         <v>8.81</v>
       </c>
       <c r="I185" s="6" t="s">
@@ -15326,7 +15332,7 @@
       <c r="G186" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="H186" s="10">
+      <c r="H186" s="8">
         <v>8.81</v>
       </c>
       <c r="I186" s="6" t="s">
@@ -15355,7 +15361,7 @@
       <c r="G187" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="H187" s="10">
+      <c r="H187" s="8">
         <v>24.52</v>
       </c>
       <c r="I187" s="6" t="s">
@@ -15384,7 +15390,7 @@
       <c r="G188" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="H188" s="10">
+      <c r="H188" s="8">
         <v>3.78</v>
       </c>
       <c r="I188" s="6" t="s">
@@ -15413,7 +15419,7 @@
       <c r="G189" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="H189" s="10">
+      <c r="H189" s="8">
         <v>3.78</v>
       </c>
       <c r="I189" s="6" t="s">
@@ -15442,7 +15448,7 @@
       <c r="G190" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="H190" s="10">
+      <c r="H190" s="8">
         <v>24.87</v>
       </c>
       <c r="I190" s="6" t="s">
@@ -15471,7 +15477,7 @@
       <c r="G191" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="H191" s="10">
+      <c r="H191" s="8">
         <v>24.87</v>
       </c>
       <c r="I191" s="6" t="s">
@@ -15500,7 +15506,7 @@
       <c r="G192" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H192" s="10">
+      <c r="H192" s="8">
         <v>7.19</v>
       </c>
       <c r="I192" s="6" t="s">
@@ -15529,7 +15535,7 @@
       <c r="G193" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H193" s="10">
+      <c r="H193" s="8">
         <v>7.19</v>
       </c>
       <c r="I193" s="6" t="s">
@@ -15558,7 +15564,7 @@
       <c r="G194" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="H194" s="10">
+      <c r="H194" s="8">
         <v>7.28</v>
       </c>
       <c r="I194" s="6" t="s">
@@ -15587,7 +15593,7 @@
       <c r="G195" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="H195" s="10">
+      <c r="H195" s="8">
         <v>7.28</v>
       </c>
       <c r="I195" s="6" t="s">
@@ -15616,7 +15622,7 @@
       <c r="G196" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="H196" s="10">
+      <c r="H196" s="8">
         <v>9.8000000000000007</v>
       </c>
       <c r="I196" s="6" t="s">
@@ -15645,7 +15651,7 @@
       <c r="G197" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="H197" s="10">
+      <c r="H197" s="8">
         <v>9.8000000000000007</v>
       </c>
       <c r="I197" s="6" t="s">
@@ -15674,7 +15680,7 @@
       <c r="G198" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H198" s="10">
+      <c r="H198" s="8">
         <v>2.77</v>
       </c>
       <c r="I198" s="6" t="s">
@@ -15703,7 +15709,7 @@
       <c r="G199" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H199" s="10">
+      <c r="H199" s="8">
         <v>2.77</v>
       </c>
       <c r="I199" s="6" t="s">
@@ -15732,7 +15738,7 @@
       <c r="G200" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="H200" s="10">
+      <c r="H200" s="8">
         <v>36.119999999999997</v>
       </c>
       <c r="I200" s="6" t="s">
@@ -15761,7 +15767,7 @@
       <c r="G201" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="H201" s="10">
+      <c r="H201" s="8">
         <v>36.119999999999997</v>
       </c>
       <c r="I201" s="6" t="s">
@@ -15788,7 +15794,7 @@
       <c r="G202" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="H202" s="10">
+      <c r="H202" s="8">
         <v>111</v>
       </c>
       <c r="I202" s="6" t="s">
@@ -15815,7 +15821,7 @@
       <c r="G203" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="H203" s="10">
+      <c r="H203" s="8">
         <v>2.2200000000000002</v>
       </c>
       <c r="I203" s="6" t="s">
@@ -15842,7 +15848,7 @@
       <c r="G204" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="H204" s="10">
+      <c r="H204" s="8">
         <v>13.64</v>
       </c>
       <c r="I204" s="6" t="s">
@@ -15871,7 +15877,7 @@
       <c r="G205" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="H205" s="10">
+      <c r="H205" s="8">
         <v>6.87</v>
       </c>
       <c r="I205" s="6" t="s">
@@ -15900,7 +15906,7 @@
       <c r="G206" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="H206" s="10">
+      <c r="H206" s="8">
         <v>6.87</v>
       </c>
       <c r="I206" s="6" t="s">
@@ -15927,7 +15933,7 @@
       <c r="G207" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H207" s="10">
+      <c r="H207" s="8">
         <v>0.47</v>
       </c>
       <c r="I207" s="6" t="s">
@@ -15956,7 +15962,7 @@
       <c r="G208" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H208" s="10">
+      <c r="H208" s="8">
         <v>38.49</v>
       </c>
       <c r="I208" s="6" t="s">
@@ -15985,7 +15991,7 @@
       <c r="G209" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H209" s="10">
+      <c r="H209" s="8">
         <v>38.49</v>
       </c>
       <c r="I209" s="6" t="s">
@@ -16012,7 +16018,7 @@
       <c r="G210" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="H210" s="10">
+      <c r="H210" s="8">
         <v>10.09</v>
       </c>
       <c r="I210" s="6" t="s">
@@ -16039,7 +16045,7 @@
       <c r="G211" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="H211" s="10">
+      <c r="H211" s="8">
         <v>10.09</v>
       </c>
       <c r="I211" s="6" t="s">
@@ -16068,7 +16074,7 @@
       <c r="G212" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H212" s="10">
+      <c r="H212" s="8">
         <v>5.43</v>
       </c>
       <c r="I212" s="6" t="s">
@@ -16097,7 +16103,7 @@
       <c r="G213" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H213" s="10">
+      <c r="H213" s="8">
         <v>5.43</v>
       </c>
       <c r="I213" s="6" t="s">
@@ -16126,7 +16132,7 @@
       <c r="G214" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="H214" s="10">
+      <c r="H214" s="8">
         <v>31.04</v>
       </c>
       <c r="I214" s="6" t="s">
@@ -16155,7 +16161,7 @@
       <c r="G215" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="H215" s="10">
+      <c r="H215" s="8">
         <v>31.04</v>
       </c>
       <c r="I215" s="6" t="s">
@@ -16182,7 +16188,7 @@
       <c r="G216" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H216" s="10">
+      <c r="H216" s="8">
         <v>2.96</v>
       </c>
       <c r="I216" s="6" t="s">
@@ -16211,7 +16217,7 @@
       <c r="G217" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H217" s="10">
+      <c r="H217" s="8">
         <v>29.23</v>
       </c>
       <c r="I217" s="6" t="s">
@@ -16240,7 +16246,7 @@
       <c r="G218" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H218" s="10">
+      <c r="H218" s="8">
         <v>29.23</v>
       </c>
       <c r="I218" s="6" t="s">
@@ -16269,7 +16275,7 @@
       <c r="G219" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="H219" s="10">
+      <c r="H219" s="8">
         <v>283.8</v>
       </c>
       <c r="I219" s="6" t="s">
@@ -16298,7 +16304,7 @@
       <c r="G220" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="H220" s="10">
+      <c r="H220" s="8">
         <v>283.8</v>
       </c>
       <c r="I220" s="6" t="s">
@@ -16327,7 +16333,7 @@
       <c r="G221" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="H221" s="10">
+      <c r="H221" s="8">
         <v>63.56</v>
       </c>
       <c r="I221" s="6" t="s">
@@ -16356,7 +16362,7 @@
       <c r="G222" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H222" s="10">
+      <c r="H222" s="8">
         <v>22.88</v>
       </c>
       <c r="I222" s="6" t="s">
@@ -16385,7 +16391,7 @@
       <c r="G223" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H223" s="10">
+      <c r="H223" s="8">
         <v>22.88</v>
       </c>
       <c r="I223" s="6" t="s">
@@ -16414,7 +16420,7 @@
       <c r="G224" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="H224" s="10">
+      <c r="H224" s="8">
         <v>286</v>
       </c>
       <c r="I224" s="6" t="s">
@@ -16443,7 +16449,7 @@
       <c r="G225" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="H225" s="10">
+      <c r="H225" s="8">
         <v>286</v>
       </c>
       <c r="I225" s="6" t="s">
@@ -16472,7 +16478,7 @@
       <c r="G226" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="H226" s="10">
+      <c r="H226" s="8">
         <v>548</v>
       </c>
       <c r="I226" s="6" t="s">
@@ -16501,7 +16507,7 @@
       <c r="G227" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="H227" s="10">
+      <c r="H227" s="8">
         <v>2790</v>
       </c>
       <c r="I227" s="6" t="s">
@@ -16526,7 +16532,7 @@
       <c r="G228" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="H228" s="10">
+      <c r="H228" s="8">
         <v>93</v>
       </c>
       <c r="I228" s="6" t="s">
@@ -16553,7 +16559,7 @@
       <c r="G229" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="H229" s="10">
+      <c r="H229" s="8">
         <v>8.2899999999999991</v>
       </c>
       <c r="I229" s="6" t="s">
@@ -16580,7 +16586,7 @@
       <c r="G230" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="H230" s="10">
+      <c r="H230" s="8">
         <v>8.2899999999999991</v>
       </c>
       <c r="I230" s="6" t="s">
@@ -16607,7 +16613,7 @@
       <c r="G231" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H231" s="10">
+      <c r="H231" s="8">
         <v>8.25</v>
       </c>
       <c r="I231" s="6" t="s">
@@ -16634,7 +16640,7 @@
       <c r="G232" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H232" s="10">
+      <c r="H232" s="8">
         <v>168</v>
       </c>
       <c r="I232" s="6" t="s">
@@ -16663,7 +16669,7 @@
       <c r="G233" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="H233" s="10">
+      <c r="H233" s="8">
         <v>50</v>
       </c>
       <c r="I233" s="6" t="s">
@@ -16692,7 +16698,7 @@
       <c r="G234" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="H234" s="10">
+      <c r="H234" s="8">
         <v>42.42</v>
       </c>
       <c r="I234" s="6" t="s">
@@ -16721,7 +16727,7 @@
       <c r="G235" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="H235" s="10">
+      <c r="H235" s="8">
         <v>42.42</v>
       </c>
       <c r="I235" s="6" t="s">
@@ -16748,7 +16754,7 @@
       <c r="G236" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="H236" s="10">
+      <c r="H236" s="8">
         <v>0.98</v>
       </c>
       <c r="I236" s="6" t="s">
@@ -16775,7 +16781,7 @@
       <c r="G237" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="H237" s="10">
+      <c r="H237" s="8">
         <v>0.98</v>
       </c>
       <c r="I237" s="6" t="s">
@@ -16802,7 +16808,7 @@
       <c r="G238" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="H238" s="10">
+      <c r="H238" s="8">
         <v>19.260000000000002</v>
       </c>
       <c r="I238" s="6" t="s">
@@ -16829,7 +16835,7 @@
       <c r="G239" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H239" s="10">
+      <c r="H239" s="8">
         <v>80.849999999999994</v>
       </c>
       <c r="I239" s="6" t="s">
@@ -16858,7 +16864,7 @@
       <c r="G240" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="H240" s="10">
+      <c r="H240" s="8">
         <v>6.85</v>
       </c>
       <c r="I240" s="6" t="s">
@@ -16887,7 +16893,7 @@
       <c r="G241" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="H241" s="10">
+      <c r="H241" s="8">
         <v>6.85</v>
       </c>
       <c r="I241" s="6" t="s">
@@ -16914,7 +16920,7 @@
       <c r="G242" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="H242" s="10">
+      <c r="H242" s="8">
         <v>160.19999999999999</v>
       </c>
       <c r="I242" s="6" t="s">
@@ -16941,7 +16947,7 @@
       <c r="G243" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="H243" s="10">
+      <c r="H243" s="8">
         <v>160.19999999999999</v>
       </c>
       <c r="I243" s="6" t="s">
@@ -16970,7 +16976,7 @@
       <c r="G244" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="H244" s="10">
+      <c r="H244" s="8">
         <v>2.4500000000000002</v>
       </c>
       <c r="I244" s="6" t="s">
@@ -16999,7 +17005,7 @@
       <c r="G245" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="H245" s="10">
+      <c r="H245" s="8">
         <v>2.4500000000000002</v>
       </c>
       <c r="I245" s="6" t="s">
@@ -17024,7 +17030,7 @@
       <c r="G246" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="H246" s="10">
+      <c r="H246" s="8">
         <v>73.5</v>
       </c>
       <c r="I246" s="6" t="s">
@@ -17053,7 +17059,7 @@
       <c r="G247" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="H247" s="10">
+      <c r="H247" s="8">
         <v>296.73</v>
       </c>
       <c r="I247" s="6" t="s">
@@ -17082,7 +17088,7 @@
       <c r="G248" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="H248" s="10">
+      <c r="H248" s="8">
         <v>296.73</v>
       </c>
       <c r="I248" s="6" t="s">
@@ -17111,7 +17117,7 @@
       <c r="G249" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="H249" s="10">
+      <c r="H249" s="8">
         <v>159.79</v>
       </c>
       <c r="I249" s="6" t="s">
@@ -17140,7 +17146,7 @@
       <c r="G250" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="H250" s="10">
+      <c r="H250" s="8">
         <v>159.79</v>
       </c>
       <c r="I250" s="6" t="s">
@@ -17167,7 +17173,7 @@
       <c r="G251" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H251" s="10">
+      <c r="H251" s="8">
         <v>32.590000000000003</v>
       </c>
       <c r="I251" s="6" t="s">
@@ -17196,7 +17202,7 @@
       <c r="G252" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="H252" s="10">
+      <c r="H252" s="8">
         <v>6.15</v>
       </c>
       <c r="I252" s="6" t="s">
@@ -17225,7 +17231,7 @@
       <c r="G253" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="H253" s="10">
+      <c r="H253" s="8">
         <v>3.2</v>
       </c>
       <c r="I253" s="6" t="s">
@@ -17254,7 +17260,7 @@
       <c r="G254" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="H254" s="10">
+      <c r="H254" s="8">
         <v>3.2</v>
       </c>
       <c r="I254" s="6" t="s">
@@ -17283,7 +17289,7 @@
       <c r="G255" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="H255" s="10">
+      <c r="H255" s="8">
         <v>2</v>
       </c>
       <c r="I255" s="6" t="s">
@@ -17312,7 +17318,7 @@
       <c r="G256" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="H256" s="10">
+      <c r="H256" s="8">
         <v>2</v>
       </c>
       <c r="I256" s="6" t="s">
@@ -17339,7 +17345,7 @@
       <c r="G257" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="H257" s="10">
+      <c r="H257" s="8">
         <v>60.21</v>
       </c>
       <c r="I257" s="6" t="s">
@@ -17364,7 +17370,7 @@
       <c r="G258" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="H258" s="10">
+      <c r="H258" s="8">
         <v>60.21</v>
       </c>
       <c r="I258" s="6" t="s">
@@ -17391,7 +17397,7 @@
       <c r="G259" s="5" t="s">
         <v>1048</v>
       </c>
-      <c r="H259" s="10">
+      <c r="H259" s="8">
         <v>46.91</v>
       </c>
       <c r="I259" s="6" t="s">
@@ -17418,7 +17424,7 @@
       <c r="G260" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="H260" s="10">
+      <c r="H260" s="8">
         <v>47.4</v>
       </c>
       <c r="I260" s="6" t="s">
@@ -17445,7 +17451,7 @@
       <c r="G261" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="H261" s="10">
+      <c r="H261" s="8">
         <v>47.4</v>
       </c>
       <c r="I261" s="6" t="s">
@@ -17472,7 +17478,7 @@
       <c r="G262" s="5" t="s">
         <v>1058</v>
       </c>
-      <c r="H262" s="10">
+      <c r="H262" s="8">
         <v>10.19</v>
       </c>
       <c r="I262" s="6" t="s">
@@ -17499,7 +17505,7 @@
       <c r="G263" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="H263" s="10">
+      <c r="H263" s="8">
         <v>8.5</v>
       </c>
       <c r="I263" s="6" t="s">
@@ -17526,7 +17532,7 @@
       <c r="G264" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="H264" s="10">
+      <c r="H264" s="8">
         <v>8.5</v>
       </c>
       <c r="I264" s="6" t="s">
@@ -17555,7 +17561,7 @@
       <c r="G265" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="H265" s="10">
+      <c r="H265" s="8">
         <v>233</v>
       </c>
       <c r="I265" s="6" t="s">
@@ -17584,7 +17590,7 @@
       <c r="G266" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="H266" s="10">
+      <c r="H266" s="8">
         <v>233</v>
       </c>
       <c r="I266" s="6" t="s">
@@ -17613,7 +17619,7 @@
       <c r="G267" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="H267" s="10">
+      <c r="H267" s="8">
         <v>229.5</v>
       </c>
       <c r="I267" s="6" t="s">
@@ -17642,7 +17648,7 @@
       <c r="G268" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="H268" s="10">
+      <c r="H268" s="8">
         <v>229.5</v>
       </c>
       <c r="I268" s="6" t="s">
@@ -17671,7 +17677,7 @@
       <c r="G269" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="H269" s="10">
+      <c r="H269" s="8">
         <v>224.79</v>
       </c>
       <c r="I269" s="6" t="s">
@@ -17698,7 +17704,7 @@
       <c r="G270" s="5" t="s">
         <v>1083</v>
       </c>
-      <c r="H270" s="10">
+      <c r="H270" s="8">
         <v>24.3</v>
       </c>
       <c r="I270" s="6" t="s">
@@ -17725,7 +17731,7 @@
       <c r="G271" s="5" t="s">
         <v>1083</v>
       </c>
-      <c r="H271" s="10">
+      <c r="H271" s="8">
         <v>24.3</v>
       </c>
       <c r="I271" s="6" t="s">
@@ -17754,7 +17760,7 @@
       <c r="G272" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="H272" s="10">
+      <c r="H272" s="8">
         <v>239</v>
       </c>
       <c r="I272" s="6" t="s">
@@ -17783,7 +17789,7 @@
       <c r="G273" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="H273" s="10">
+      <c r="H273" s="8">
         <v>239</v>
       </c>
       <c r="I273" s="6" t="s">
@@ -17810,7 +17816,7 @@
       <c r="G274" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="H274" s="10">
+      <c r="H274" s="8">
         <v>232</v>
       </c>
       <c r="I274" s="6" t="s">
@@ -17835,7 +17841,7 @@
       <c r="G275" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="H275" s="10">
+      <c r="H275" s="8">
         <v>232</v>
       </c>
       <c r="I275" s="6" t="s">
@@ -17862,7 +17868,7 @@
       <c r="G276" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="H276" s="10">
+      <c r="H276" s="8">
         <v>52.41</v>
       </c>
       <c r="I276" s="6" t="s">
@@ -17889,7 +17895,7 @@
       <c r="G277" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="H277" s="10">
+      <c r="H277" s="8">
         <v>52.41</v>
       </c>
       <c r="I277" s="6" t="s">
@@ -17918,7 +17924,7 @@
       <c r="G278" s="5" t="s">
         <v>1107</v>
       </c>
-      <c r="H278" s="10">
+      <c r="H278" s="8">
         <v>23.77</v>
       </c>
       <c r="I278" s="6" t="s">
@@ -17947,7 +17953,7 @@
       <c r="G279" s="5" t="s">
         <v>1107</v>
       </c>
-      <c r="H279" s="10">
+      <c r="H279" s="8">
         <v>23.77</v>
       </c>
       <c r="I279" s="6" t="s">
@@ -17976,7 +17982,7 @@
       <c r="G280" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="H280" s="10">
+      <c r="H280" s="8">
         <v>1.8</v>
       </c>
       <c r="I280" s="6" t="s">
@@ -18005,7 +18011,7 @@
       <c r="G281" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="H281" s="10">
+      <c r="H281" s="8">
         <v>1.8</v>
       </c>
       <c r="I281" s="6" t="s">
@@ -18034,7 +18040,7 @@
       <c r="G282" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="H282" s="10">
+      <c r="H282" s="8">
         <v>8.39</v>
       </c>
       <c r="I282" s="6" t="s">
@@ -18061,7 +18067,7 @@
       <c r="G283" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H283" s="10">
+      <c r="H283" s="8">
         <v>59.2</v>
       </c>
       <c r="I283" s="6" t="s">
@@ -18088,7 +18094,7 @@
       <c r="G284" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="H284" s="10">
+      <c r="H284" s="8">
         <v>43.5</v>
       </c>
       <c r="I284" s="6" t="s">
@@ -18113,7 +18119,7 @@
       <c r="G285" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="H285" s="10">
+      <c r="H285" s="8">
         <v>43.5</v>
       </c>
       <c r="I285" s="6" t="s">
@@ -18140,7 +18146,7 @@
       <c r="G286" s="5" t="s">
         <v>1135</v>
       </c>
-      <c r="H286" s="10">
+      <c r="H286" s="8">
         <v>65.17</v>
       </c>
       <c r="I286" s="6" t="s">
@@ -18167,7 +18173,7 @@
       <c r="G287" s="5" t="s">
         <v>1135</v>
       </c>
-      <c r="H287" s="10">
+      <c r="H287" s="8">
         <v>65.17</v>
       </c>
       <c r="I287" s="6" t="s">
@@ -18194,7 +18200,7 @@
       <c r="G288" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="H288" s="10">
+      <c r="H288" s="8">
         <v>23.8</v>
       </c>
       <c r="I288" s="6" t="s">
@@ -18223,7 +18229,7 @@
       <c r="G289" s="5" t="s">
         <v>1148</v>
       </c>
-      <c r="H289" s="10">
+      <c r="H289" s="8">
         <v>68.37</v>
       </c>
       <c r="I289" s="6" t="s">
@@ -18252,7 +18258,7 @@
       <c r="G290" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H290" s="10">
+      <c r="H290" s="8">
         <v>57.35</v>
       </c>
       <c r="I290" s="6" t="s">
@@ -18281,7 +18287,7 @@
       <c r="G291" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="H291" s="10">
+      <c r="H291" s="8">
         <v>33.9</v>
       </c>
       <c r="I291" s="6" t="s">
@@ -18310,7 +18316,7 @@
       <c r="G292" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="H292" s="10">
+      <c r="H292" s="8">
         <v>33.9</v>
       </c>
       <c r="I292" s="6" t="s">
@@ -18337,7 +18343,7 @@
       <c r="G293" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="H293" s="10">
+      <c r="H293" s="8">
         <v>4.0599999999999996</v>
       </c>
       <c r="I293" s="6" t="s">
@@ -18362,7 +18368,7 @@
       <c r="G294" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="H294" s="10">
+      <c r="H294" s="8">
         <v>4.0599999999999996</v>
       </c>
       <c r="I294" s="6" t="s">
@@ -18391,7 +18397,7 @@
       <c r="G295" s="5" t="s">
         <v>1169</v>
       </c>
-      <c r="H295" s="10">
+      <c r="H295" s="8">
         <v>26.38</v>
       </c>
       <c r="I295" s="6" t="s">
@@ -18420,7 +18426,7 @@
       <c r="G296" s="5" t="s">
         <v>1169</v>
       </c>
-      <c r="H296" s="10">
+      <c r="H296" s="8">
         <v>26.38</v>
       </c>
       <c r="I296" s="6" t="s">
@@ -18449,7 +18455,7 @@
       <c r="G297" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="H297" s="10">
+      <c r="H297" s="8">
         <v>18.25</v>
       </c>
       <c r="I297" s="6" t="s">
@@ -18476,7 +18482,7 @@
       <c r="G298" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="H298" s="10">
+      <c r="H298" s="8">
         <v>7.38</v>
       </c>
       <c r="I298" s="6" t="s">
@@ -18503,7 +18509,7 @@
       <c r="G299" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="H299" s="10">
+      <c r="H299" s="8">
         <v>7.38</v>
       </c>
       <c r="I299" s="6" t="s">
@@ -18532,7 +18538,7 @@
       <c r="G300" s="5" t="s">
         <v>1187</v>
       </c>
-      <c r="H300" s="10">
+      <c r="H300" s="8">
         <v>23.42</v>
       </c>
       <c r="I300" s="6" t="s">
@@ -18559,7 +18565,7 @@
       <c r="G301" s="5" t="s">
         <v>1192</v>
       </c>
-      <c r="H301" s="10">
+      <c r="H301" s="8">
         <v>2.06</v>
       </c>
       <c r="I301" s="6" t="s">
@@ -18586,7 +18592,7 @@
       <c r="G302" s="5" t="s">
         <v>1192</v>
       </c>
-      <c r="H302" s="10">
+      <c r="H302" s="8">
         <v>2.06</v>
       </c>
       <c r="I302" s="6" t="s">
@@ -18613,7 +18619,7 @@
       <c r="G303" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="H303" s="10">
+      <c r="H303" s="8">
         <v>11.41</v>
       </c>
       <c r="I303" s="6" t="s">
@@ -18640,7 +18646,7 @@
       <c r="G304" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="H304" s="10">
+      <c r="H304" s="8">
         <v>11.41</v>
       </c>
       <c r="I304" s="6" t="s">
@@ -18667,7 +18673,7 @@
       <c r="G305" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="H305" s="10">
+      <c r="H305" s="8">
         <v>24.05</v>
       </c>
       <c r="I305" s="6" t="s">
@@ -18694,7 +18700,7 @@
       <c r="G306" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="H306" s="10">
+      <c r="H306" s="8">
         <v>24.05</v>
       </c>
       <c r="I306" s="6" t="s">
@@ -18723,7 +18729,7 @@
       <c r="G307" s="5" t="s">
         <v>1206</v>
       </c>
-      <c r="H307" s="10">
+      <c r="H307" s="8">
         <v>78.5</v>
       </c>
       <c r="I307" s="6" t="s">
@@ -18752,7 +18758,7 @@
       <c r="G308" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="H308" s="10">
+      <c r="H308" s="8">
         <v>69.3</v>
       </c>
       <c r="I308" s="6" t="s">
@@ -18781,7 +18787,7 @@
       <c r="G309" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="H309" s="10">
+      <c r="H309" s="8">
         <v>69.3</v>
       </c>
       <c r="I309" s="6" t="s">
@@ -18810,7 +18816,7 @@
       <c r="G310" s="5" t="s">
         <v>1219</v>
       </c>
-      <c r="H310" s="10">
+      <c r="H310" s="8">
         <v>38.75</v>
       </c>
       <c r="I310" s="6" t="s">
@@ -18839,7 +18845,7 @@
       <c r="G311" s="5" t="s">
         <v>1219</v>
       </c>
-      <c r="H311" s="10">
+      <c r="H311" s="8">
         <v>38.75</v>
       </c>
       <c r="I311" s="6" t="s">
@@ -18866,7 +18872,7 @@
       <c r="G312" s="5" t="s">
         <v>1223</v>
       </c>
-      <c r="H312" s="10">
+      <c r="H312" s="8">
         <v>28.24</v>
       </c>
       <c r="I312" s="6" t="s">
@@ -18893,7 +18899,7 @@
       <c r="G313" s="5" t="s">
         <v>1223</v>
       </c>
-      <c r="H313" s="10">
+      <c r="H313" s="8">
         <v>28.24</v>
       </c>
       <c r="I313" s="6" t="s">
@@ -18920,7 +18926,7 @@
       <c r="G314" s="5" t="s">
         <v>1229</v>
       </c>
-      <c r="H314" s="10">
+      <c r="H314" s="8">
         <v>3.97</v>
       </c>
       <c r="I314" s="6" t="s">
@@ -18949,7 +18955,7 @@
       <c r="G315" s="5" t="s">
         <v>1235</v>
       </c>
-      <c r="H315" s="10">
+      <c r="H315" s="8">
         <v>30.15</v>
       </c>
       <c r="I315" s="6" t="s">
@@ -18978,7 +18984,7 @@
       <c r="G316" s="5" t="s">
         <v>1235</v>
       </c>
-      <c r="H316" s="10">
+      <c r="H316" s="8">
         <v>30.15</v>
       </c>
       <c r="I316" s="6" t="s">
@@ -19007,7 +19013,7 @@
       <c r="G317" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="H317" s="10">
+      <c r="H317" s="8">
         <v>17.55</v>
       </c>
       <c r="I317" s="6" t="s">
@@ -19036,7 +19042,7 @@
       <c r="G318" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="H318" s="10">
+      <c r="H318" s="8">
         <v>4.05</v>
       </c>
       <c r="I318" s="6" t="s">
@@ -19063,7 +19069,7 @@
       <c r="G319" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H319" s="10">
+      <c r="H319" s="8">
         <v>8.98</v>
       </c>
       <c r="I319" s="6" t="s">
@@ -19090,7 +19096,7 @@
       <c r="G320" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="H320" s="10">
+      <c r="H320" s="8">
         <v>187</v>
       </c>
       <c r="I320" s="6" t="s">
@@ -19119,7 +19125,7 @@
       <c r="G321" s="5" t="s">
         <v>1259</v>
       </c>
-      <c r="H321" s="10">
+      <c r="H321" s="8">
         <v>156.80000000000001</v>
       </c>
       <c r="I321" s="6" t="s">
@@ -19146,7 +19152,7 @@
       <c r="G322" s="5" t="s">
         <v>1264</v>
       </c>
-      <c r="H322" s="10">
+      <c r="H322" s="8">
         <v>0.56999999999999995</v>
       </c>
       <c r="I322" s="6" t="s">
@@ -19173,7 +19179,7 @@
       <c r="G323" s="5" t="s">
         <v>1264</v>
       </c>
-      <c r="H323" s="10">
+      <c r="H323" s="8">
         <v>0.56999999999999995</v>
       </c>
       <c r="I323" s="6" t="s">
@@ -19200,7 +19206,7 @@
       <c r="G324" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="H324" s="10">
+      <c r="H324" s="8">
         <v>12.8</v>
       </c>
       <c r="I324" s="6" t="s">
@@ -19227,7 +19233,7 @@
       <c r="G325" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="H325" s="10">
+      <c r="H325" s="8">
         <v>50.26</v>
       </c>
       <c r="I325" s="6" t="s">
@@ -19254,7 +19260,7 @@
       <c r="G326" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="H326" s="10">
+      <c r="H326" s="8">
         <v>50.26</v>
       </c>
       <c r="I326" s="6" t="s">
@@ -19283,7 +19289,7 @@
       <c r="G327" s="5" t="s">
         <v>1280</v>
       </c>
-      <c r="H327" s="10">
+      <c r="H327" s="8">
         <v>25.31</v>
       </c>
       <c r="I327" s="6" t="s">
@@ -19312,7 +19318,7 @@
       <c r="G328" s="5" t="s">
         <v>1280</v>
       </c>
-      <c r="H328" s="10">
+      <c r="H328" s="8">
         <v>25.31</v>
       </c>
       <c r="I328" s="6" t="s">
@@ -19341,7 +19347,7 @@
       <c r="G329" s="5" t="s">
         <v>1287</v>
       </c>
-      <c r="H329" s="10">
+      <c r="H329" s="8">
         <v>33</v>
       </c>
       <c r="I329" s="6" t="s">
@@ -19370,7 +19376,7 @@
       <c r="G330" s="5" t="s">
         <v>1287</v>
       </c>
-      <c r="H330" s="10">
+      <c r="H330" s="8">
         <v>33</v>
       </c>
       <c r="I330" s="6" t="s">
@@ -19399,7 +19405,7 @@
       <c r="G331" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H331" s="10">
+      <c r="H331" s="8">
         <v>4.12</v>
       </c>
       <c r="I331" s="6" t="s">
@@ -19428,7 +19434,7 @@
       <c r="G332" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H332" s="10">
+      <c r="H332" s="8">
         <v>4.12</v>
       </c>
       <c r="I332" s="6" t="s">
@@ -19457,7 +19463,7 @@
       <c r="G333" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H333" s="10">
+      <c r="H333" s="8">
         <v>30.97</v>
       </c>
       <c r="I333" s="6" t="s">
@@ -19486,7 +19492,7 @@
       <c r="G334" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H334" s="10">
+      <c r="H334" s="8">
         <v>30.97</v>
       </c>
       <c r="I334" s="6" t="s">
@@ -19515,7 +19521,7 @@
       <c r="G335" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="H335" s="10">
+      <c r="H335" s="8">
         <v>20.86</v>
       </c>
       <c r="I335" s="6" t="s">
@@ -19542,7 +19548,7 @@
       <c r="G336" s="5" t="s">
         <v>1310</v>
       </c>
-      <c r="H336" s="10">
+      <c r="H336" s="8">
         <v>26.4</v>
       </c>
       <c r="I336" s="6" t="s">
@@ -19569,7 +19575,7 @@
       <c r="G337" s="5" t="s">
         <v>1310</v>
       </c>
-      <c r="H337" s="10">
+      <c r="H337" s="8">
         <v>26.4</v>
       </c>
       <c r="I337" s="6" t="s">
@@ -19596,7 +19602,7 @@
       <c r="G338" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="H338" s="10">
+      <c r="H338" s="8">
         <v>8.0399999999999991</v>
       </c>
       <c r="I338" s="6" t="s">
@@ -19623,7 +19629,7 @@
       <c r="G339" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="H339" s="10">
+      <c r="H339" s="8">
         <v>17.38</v>
       </c>
       <c r="I339" s="6" t="s">
@@ -19650,7 +19656,7 @@
       <c r="G340" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="H340" s="10">
+      <c r="H340" s="8">
         <v>17.38</v>
       </c>
       <c r="I340" s="6" t="s">
@@ -19679,7 +19685,7 @@
       <c r="G341" s="5" t="s">
         <v>1328</v>
       </c>
-      <c r="H341" s="10">
+      <c r="H341" s="8">
         <v>11.16</v>
       </c>
       <c r="I341" s="6" t="s">
@@ -19706,7 +19712,7 @@
       <c r="G342" s="5" t="s">
         <v>1333</v>
       </c>
-      <c r="H342" s="10">
+      <c r="H342" s="8">
         <v>17.59</v>
       </c>
       <c r="I342" s="6" t="s">
@@ -19733,7 +19739,7 @@
       <c r="G343" s="5" t="s">
         <v>1333</v>
       </c>
-      <c r="H343" s="10">
+      <c r="H343" s="8">
         <v>17.59</v>
       </c>
       <c r="I343" s="6" t="s">
@@ -19760,7 +19766,7 @@
       <c r="G344" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="H344" s="10">
+      <c r="H344" s="8">
         <v>148</v>
       </c>
       <c r="I344" s="6" t="s">
@@ -19787,7 +19793,7 @@
       <c r="G345" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="H345" s="10">
+      <c r="H345" s="8">
         <v>148</v>
       </c>
       <c r="I345" s="6" t="s">
@@ -19814,7 +19820,7 @@
       <c r="G346" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="H346" s="10">
+      <c r="H346" s="8">
         <v>12.83</v>
       </c>
       <c r="I346" s="6" t="s">
@@ -19841,7 +19847,7 @@
       <c r="G347" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="H347" s="10">
+      <c r="H347" s="8">
         <v>12.83</v>
       </c>
       <c r="I347" s="6" t="s">
@@ -19870,7 +19876,7 @@
       <c r="G348" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H348" s="10">
+      <c r="H348" s="8">
         <v>90.16</v>
       </c>
       <c r="I348" s="6" t="s">
@@ -19897,7 +19903,7 @@
       <c r="G349" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="H349" s="10">
+      <c r="H349" s="8">
         <v>63.28</v>
       </c>
       <c r="I349" s="6" t="s">
@@ -19926,7 +19932,7 @@
       <c r="G350" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="H350" s="10">
+      <c r="H350" s="8">
         <v>56.51</v>
       </c>
       <c r="I350" s="6" t="s">
@@ -19955,7 +19961,7 @@
       <c r="G351" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="H351" s="10">
+      <c r="H351" s="8">
         <v>56.51</v>
       </c>
       <c r="I351" s="6" t="s">
@@ -19984,7 +19990,7 @@
       <c r="G352" s="5" t="s">
         <v>1367</v>
       </c>
-      <c r="H352" s="10">
+      <c r="H352" s="8">
         <v>34.24</v>
       </c>
       <c r="I352" s="6" t="s">
@@ -20013,7 +20019,7 @@
       <c r="G353" s="5" t="s">
         <v>1367</v>
       </c>
-      <c r="H353" s="10">
+      <c r="H353" s="8">
         <v>34.24</v>
       </c>
       <c r="I353" s="6" t="s">
@@ -20042,7 +20048,7 @@
       <c r="G354" s="5" t="s">
         <v>1374</v>
       </c>
-      <c r="H354" s="10">
+      <c r="H354" s="8">
         <v>54.07</v>
       </c>
       <c r="I354" s="6" t="s">
@@ -20071,7 +20077,7 @@
       <c r="G355" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H355" s="10">
+      <c r="H355" s="8">
         <v>30.96</v>
       </c>
       <c r="I355" s="6" t="s">
@@ -20100,7 +20106,7 @@
       <c r="G356" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H356" s="10">
+      <c r="H356" s="8">
         <v>30.96</v>
       </c>
       <c r="I356" s="6" t="s">
@@ -20129,7 +20135,7 @@
       <c r="G357" s="5" t="s">
         <v>1389</v>
       </c>
-      <c r="H357" s="10">
+      <c r="H357" s="8">
         <v>29.15</v>
       </c>
       <c r="I357" s="6" t="s">
@@ -20158,7 +20164,7 @@
       <c r="G358" s="5" t="s">
         <v>1389</v>
       </c>
-      <c r="H358" s="10">
+      <c r="H358" s="8">
         <v>29.15</v>
       </c>
       <c r="I358" s="6" t="s">
@@ -20187,7 +20193,7 @@
       <c r="G359" s="5" t="s">
         <v>1396</v>
       </c>
-      <c r="H359" s="10">
+      <c r="H359" s="8">
         <v>39.5</v>
       </c>
       <c r="I359" s="6" t="s">
@@ -20214,7 +20220,7 @@
       <c r="G360" s="5" t="s">
         <v>1402</v>
       </c>
-      <c r="H360" s="10">
+      <c r="H360" s="8">
         <v>878.22</v>
       </c>
       <c r="I360" s="6" t="s">
@@ -20243,7 +20249,7 @@
       <c r="G361" s="5" t="s">
         <v>1408</v>
       </c>
-      <c r="H361" s="10">
+      <c r="H361" s="8">
         <v>42.67</v>
       </c>
       <c r="I361" s="6" t="s">
@@ -20270,7 +20276,7 @@
       <c r="G362" s="5" t="s">
         <v>1413</v>
       </c>
-      <c r="H362" s="10">
+      <c r="H362" s="8">
         <v>424.43</v>
       </c>
       <c r="I362" s="6" t="s">
@@ -20297,7 +20303,7 @@
       <c r="G363" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="H363" s="10">
+      <c r="H363" s="8">
         <v>13.8</v>
       </c>
       <c r="I363" s="6" t="s">
@@ -20324,7 +20330,7 @@
       <c r="G364" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="H364" s="10">
+      <c r="H364" s="8">
         <v>13.8</v>
       </c>
       <c r="I364" s="6" t="s">
@@ -20351,7 +20357,7 @@
       <c r="G365" s="5" t="s">
         <v>1423</v>
       </c>
-      <c r="H365" s="10">
+      <c r="H365" s="8">
         <v>2.6</v>
       </c>
       <c r="I365" s="6" t="s">
@@ -20376,7 +20382,7 @@
       <c r="G366" s="5" t="s">
         <v>1423</v>
       </c>
-      <c r="H366" s="10">
+      <c r="H366" s="8">
         <v>2.6</v>
       </c>
       <c r="I366" s="6" t="s">
@@ -20403,7 +20409,7 @@
       <c r="G367" s="5" t="s">
         <v>1374</v>
       </c>
-      <c r="H367" s="10">
+      <c r="H367" s="8">
         <v>1.59</v>
       </c>
       <c r="I367" s="6" t="s">
@@ -20432,7 +20438,7 @@
       <c r="G368" s="5" t="s">
         <v>1431</v>
       </c>
-      <c r="H368" s="10">
+      <c r="H368" s="8">
         <v>17.440000000000001</v>
       </c>
       <c r="I368" s="6" t="s">
@@ -20461,7 +20467,7 @@
       <c r="G369" s="5" t="s">
         <v>1431</v>
       </c>
-      <c r="H369" s="10">
+      <c r="H369" s="8">
         <v>17.440000000000001</v>
       </c>
       <c r="I369" s="6" t="s">
@@ -20488,7 +20494,7 @@
       <c r="G370" s="5" t="s">
         <v>1434</v>
       </c>
-      <c r="H370" s="10">
+      <c r="H370" s="8">
         <v>14.5</v>
       </c>
       <c r="I370" s="6" t="s">
@@ -20515,7 +20521,7 @@
       <c r="G371" s="5" t="s">
         <v>1434</v>
       </c>
-      <c r="H371" s="10">
+      <c r="H371" s="8">
         <v>14.5</v>
       </c>
       <c r="I371" s="6" t="s">
@@ -20542,7 +20548,7 @@
       <c r="G372" s="5" t="s">
         <v>1438</v>
       </c>
-      <c r="H372" s="10">
+      <c r="H372" s="8">
         <v>26.79</v>
       </c>
       <c r="I372" s="6" t="s">
@@ -20571,7 +20577,7 @@
       <c r="G373" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H373" s="10">
+      <c r="H373" s="8">
         <v>294.26</v>
       </c>
       <c r="I373" s="6" t="s">
@@ -20600,7 +20606,7 @@
       <c r="G374" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="H374" s="10">
+      <c r="H374" s="8">
         <v>90.3</v>
       </c>
       <c r="I374" s="6" t="s">
@@ -20629,7 +20635,7 @@
       <c r="G375" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="H375" s="10">
+      <c r="H375" s="8">
         <v>90.3</v>
       </c>
       <c r="I375" s="6" t="s">
@@ -20658,7 +20664,7 @@
       <c r="G376" s="5" t="s">
         <v>1454</v>
       </c>
-      <c r="H376" s="10">
+      <c r="H376" s="8">
         <v>6.87</v>
       </c>
       <c r="I376" s="6" t="s">
@@ -20687,7 +20693,7 @@
       <c r="G377" s="5" t="s">
         <v>1454</v>
       </c>
-      <c r="H377" s="10">
+      <c r="H377" s="8">
         <v>6.87</v>
       </c>
       <c r="I377" s="6" t="s">
@@ -20716,7 +20722,7 @@
       <c r="G378" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H378" s="10">
+      <c r="H378" s="8">
         <v>54.79</v>
       </c>
       <c r="I378" s="6" t="s">
@@ -20745,7 +20751,7 @@
       <c r="G379" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H379" s="10">
+      <c r="H379" s="8">
         <v>54.79</v>
       </c>
       <c r="I379" s="6" t="s">
@@ -20774,7 +20780,7 @@
       <c r="G380" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H380" s="10">
+      <c r="H380" s="8">
         <v>37.64</v>
       </c>
       <c r="I380" s="6" t="s">
@@ -20801,7 +20807,7 @@
       <c r="G381" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H381" s="10">
+      <c r="H381" s="8">
         <v>37.64</v>
       </c>
       <c r="I381" s="6" t="s">
@@ -20828,7 +20834,7 @@
       <c r="G382" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="H382" s="10">
+      <c r="H382" s="8">
         <v>7.15</v>
       </c>
       <c r="I382" s="6" t="s">
@@ -20855,7 +20861,7 @@
       <c r="G383" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="H383" s="10">
+      <c r="H383" s="8">
         <v>7.15</v>
       </c>
       <c r="I383" s="6" t="s">
@@ -20884,7 +20890,7 @@
       <c r="G384" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="H384" s="10">
+      <c r="H384" s="8">
         <v>90</v>
       </c>
       <c r="I384" s="6" t="s">
@@ -20913,7 +20919,7 @@
       <c r="G385" s="5" t="s">
         <v>1482</v>
       </c>
-      <c r="H385" s="10">
+      <c r="H385" s="8">
         <v>97.2</v>
       </c>
       <c r="I385" s="6" t="s">
@@ -20942,7 +20948,7 @@
       <c r="G386" s="5" t="s">
         <v>1488</v>
       </c>
-      <c r="H386" s="10">
+      <c r="H386" s="8">
         <v>7.3</v>
       </c>
       <c r="I386" s="6" t="s">
@@ -20971,7 +20977,7 @@
       <c r="G387" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H387" s="10">
+      <c r="H387" s="8">
         <v>53.18</v>
       </c>
       <c r="I387" s="6" t="s">
@@ -20998,7 +21004,7 @@
       <c r="G388" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="H388" s="10">
+      <c r="H388" s="8">
         <v>22.91</v>
       </c>
       <c r="I388" s="6" t="s">
@@ -21025,7 +21031,7 @@
       <c r="G389" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="H389" s="10">
+      <c r="H389" s="8">
         <v>22.91</v>
       </c>
       <c r="I389" s="6" t="s">
@@ -21052,7 +21058,7 @@
       <c r="G390" s="5" t="s">
         <v>1504</v>
       </c>
-      <c r="H390" s="10">
+      <c r="H390" s="8">
         <v>74.8</v>
       </c>
       <c r="I390" s="6" t="s">
@@ -21079,7 +21085,7 @@
       <c r="G391" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H391" s="10">
+      <c r="H391" s="8">
         <v>15.2</v>
       </c>
       <c r="I391" s="6" t="s">
@@ -21108,7 +21114,7 @@
       <c r="G392" s="5" t="s">
         <v>1514</v>
       </c>
-      <c r="H392" s="10">
+      <c r="H392" s="8">
         <v>12.3</v>
       </c>
       <c r="I392" s="6" t="s">
@@ -21135,7 +21141,7 @@
       <c r="G393" s="5" t="s">
         <v>1520</v>
       </c>
-      <c r="H393" s="10">
+      <c r="H393" s="8">
         <v>6.45</v>
       </c>
       <c r="I393" s="6" t="s">
@@ -21162,7 +21168,7 @@
       <c r="G394" s="5" t="s">
         <v>1520</v>
       </c>
-      <c r="H394" s="10">
+      <c r="H394" s="8">
         <v>6.45</v>
       </c>
       <c r="I394" s="6" t="s">
@@ -21191,7 +21197,7 @@
       <c r="G395" s="5" t="s">
         <v>1514</v>
       </c>
-      <c r="H395" s="10">
+      <c r="H395" s="8">
         <v>11.67</v>
       </c>
       <c r="I395" s="6" t="s">
@@ -21220,7 +21226,7 @@
       <c r="G396" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H396" s="10">
+      <c r="H396" s="8">
         <v>169.38</v>
       </c>
       <c r="I396" s="6" t="s">
@@ -21249,7 +21255,7 @@
       <c r="G397" s="5" t="s">
         <v>1535</v>
       </c>
-      <c r="H397" s="10">
+      <c r="H397" s="8">
         <v>6.4</v>
       </c>
       <c r="I397" s="6" t="s">
@@ -21278,7 +21284,7 @@
       <c r="G398" s="5" t="s">
         <v>1535</v>
       </c>
-      <c r="H398" s="10">
+      <c r="H398" s="8">
         <v>6.4</v>
       </c>
       <c r="I398" s="6" t="s">
@@ -21307,7 +21313,7 @@
       <c r="G399" s="5" t="s">
         <v>1541</v>
       </c>
-      <c r="H399" s="10">
+      <c r="H399" s="8">
         <v>35.799999999999997</v>
       </c>
       <c r="I399" s="6" t="s">
@@ -21336,7 +21342,7 @@
       <c r="G400" s="5" t="s">
         <v>1541</v>
       </c>
-      <c r="H400" s="10">
+      <c r="H400" s="8">
         <v>35.799999999999997</v>
       </c>
       <c r="I400" s="6" t="s">
@@ -21363,7 +21369,7 @@
       <c r="G401" s="5" t="s">
         <v>1545</v>
       </c>
-      <c r="H401" s="10">
+      <c r="H401" s="8">
         <v>36.340000000000003</v>
       </c>
       <c r="I401" s="6" t="s">
@@ -21392,7 +21398,7 @@
       <c r="G402" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H402" s="10">
+      <c r="H402" s="8">
         <v>13.55</v>
       </c>
       <c r="I402" s="6" t="s">
@@ -21421,7 +21427,7 @@
       <c r="G403" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H403" s="10">
+      <c r="H403" s="8">
         <v>13.55</v>
       </c>
       <c r="I403" s="6" t="s">
@@ -21448,7 +21454,7 @@
       <c r="G404" s="5" t="s">
         <v>1554</v>
       </c>
-      <c r="H404" s="10">
+      <c r="H404" s="8">
         <v>1.45</v>
       </c>
       <c r="I404" s="6" t="s">
@@ -21475,7 +21481,7 @@
       <c r="G405" s="5" t="s">
         <v>1554</v>
       </c>
-      <c r="H405" s="10">
+      <c r="H405" s="8">
         <v>1.45</v>
       </c>
       <c r="I405" s="6" t="s">
@@ -21502,7 +21508,7 @@
       <c r="G406" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H406" s="10">
+      <c r="H406" s="8">
         <v>86.64</v>
       </c>
       <c r="I406" s="6" t="s">
@@ -21529,7 +21535,7 @@
       <c r="G407" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H407" s="10">
+      <c r="H407" s="8">
         <v>86.64</v>
       </c>
       <c r="I407" s="6" t="s">
@@ -21556,7 +21562,7 @@
       <c r="G408" s="5" t="s">
         <v>1566</v>
       </c>
-      <c r="H408" s="10">
+      <c r="H408" s="8">
         <v>4.5999999999999996</v>
       </c>
       <c r="I408" s="6" t="s">
@@ -21583,7 +21589,7 @@
       <c r="G409" s="5" t="s">
         <v>1566</v>
       </c>
-      <c r="H409" s="10">
+      <c r="H409" s="8">
         <v>4.5999999999999996</v>
       </c>
       <c r="I409" s="6" t="s">
@@ -21612,7 +21618,7 @@
       <c r="G410" s="5" t="s">
         <v>1572</v>
       </c>
-      <c r="H410" s="10">
+      <c r="H410" s="8">
         <v>17.809999999999999</v>
       </c>
       <c r="I410" s="6" t="s">
@@ -21641,7 +21647,7 @@
       <c r="G411" s="5" t="s">
         <v>1572</v>
       </c>
-      <c r="H411" s="10">
+      <c r="H411" s="8">
         <v>17.809999999999999</v>
       </c>
       <c r="I411" s="6" t="s">
@@ -21668,7 +21674,7 @@
       <c r="G412" s="5" t="s">
         <v>1577</v>
       </c>
-      <c r="H412" s="10">
+      <c r="H412" s="8">
         <v>13.64</v>
       </c>
       <c r="I412" s="6" t="s">
@@ -21695,7 +21701,7 @@
       <c r="G413" s="5" t="s">
         <v>1577</v>
       </c>
-      <c r="H413" s="10">
+      <c r="H413" s="8">
         <v>13.64</v>
       </c>
       <c r="I413" s="6" t="s">
@@ -21724,7 +21730,7 @@
       <c r="G414" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H414" s="10">
+      <c r="H414" s="8">
         <v>94.64</v>
       </c>
       <c r="I414" s="6" t="s">
@@ -21753,7 +21759,7 @@
       <c r="G415" s="5" t="s">
         <v>1589</v>
       </c>
-      <c r="H415" s="10">
+      <c r="H415" s="8">
         <v>7.02</v>
       </c>
       <c r="I415" s="6" t="s">
@@ -21782,7 +21788,7 @@
       <c r="G416" s="5" t="s">
         <v>1589</v>
       </c>
-      <c r="H416" s="10">
+      <c r="H416" s="8">
         <v>7.02</v>
       </c>
       <c r="I416" s="6" t="s">
@@ -21809,7 +21815,7 @@
       <c r="G417" s="5" t="s">
         <v>1596</v>
       </c>
-      <c r="H417" s="10">
+      <c r="H417" s="8">
         <v>80</v>
       </c>
       <c r="I417" s="6" t="s">
@@ -21838,7 +21844,7 @@
       <c r="G418" s="5" t="s">
         <v>1602</v>
       </c>
-      <c r="H418" s="10">
+      <c r="H418" s="8">
         <v>1008</v>
       </c>
       <c r="I418" s="6" t="s">
@@ -21867,7 +21873,7 @@
       <c r="G419" s="5" t="s">
         <v>1608</v>
       </c>
-      <c r="H419" s="10">
+      <c r="H419" s="8">
         <v>2969.35</v>
       </c>
       <c r="I419" s="6" t="s">
@@ -21896,7 +21902,7 @@
       <c r="G420" s="5" t="s">
         <v>1608</v>
       </c>
-      <c r="H420" s="10">
+      <c r="H420" s="8">
         <v>2135.44</v>
       </c>
       <c r="I420" s="6" t="s">
@@ -21925,7 +21931,7 @@
       <c r="G421" s="5" t="s">
         <v>1618</v>
       </c>
-      <c r="H421" s="10">
+      <c r="H421" s="8">
         <v>1512.91</v>
       </c>
       <c r="I421" s="6" t="s">
@@ -21954,7 +21960,7 @@
       <c r="G422" s="5" t="s">
         <v>1624</v>
       </c>
-      <c r="H422" s="10">
+      <c r="H422" s="8">
         <v>113.75</v>
       </c>
       <c r="I422" s="6" t="s">
@@ -21983,7 +21989,7 @@
       <c r="G423" s="5" t="s">
         <v>1624</v>
       </c>
-      <c r="H423" s="10">
+      <c r="H423" s="8">
         <v>113.75</v>
       </c>
       <c r="I423" s="6" t="s">
@@ -22012,7 +22018,7 @@
       <c r="G424" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="H424" s="10">
+      <c r="H424" s="8">
         <v>64.489999999999995</v>
       </c>
       <c r="I424" s="6" t="s">
@@ -22041,7 +22047,7 @@
       <c r="G425" s="5" t="s">
         <v>1636</v>
       </c>
-      <c r="H425" s="10">
+      <c r="H425" s="8">
         <v>9.3699999999999992</v>
       </c>
       <c r="I425" s="6" t="s">
@@ -22070,7 +22076,7 @@
       <c r="G426" s="5" t="s">
         <v>1643</v>
       </c>
-      <c r="H426" s="10">
+      <c r="H426" s="8">
         <v>326.10000000000002</v>
       </c>
       <c r="I426" s="6" t="s">
@@ -22097,7 +22103,7 @@
       <c r="G427" s="5" t="s">
         <v>1648</v>
       </c>
-      <c r="H427" s="10">
+      <c r="H427" s="8">
         <v>1.8</v>
       </c>
       <c r="I427" s="6" t="s">
@@ -22124,7 +22130,7 @@
       <c r="G428" s="5" t="s">
         <v>1648</v>
       </c>
-      <c r="H428" s="10">
+      <c r="H428" s="8">
         <v>1.8</v>
       </c>
       <c r="I428" s="6" t="s">
@@ -22151,7 +22157,7 @@
       <c r="G429" s="5" t="s">
         <v>1655</v>
       </c>
-      <c r="H429" s="10">
+      <c r="H429" s="8">
         <v>7.13</v>
       </c>
       <c r="I429" s="6" t="s">
@@ -22180,7 +22186,7 @@
       <c r="G430" s="5" t="s">
         <v>1661</v>
       </c>
-      <c r="H430" s="10">
+      <c r="H430" s="8">
         <v>6.68</v>
       </c>
       <c r="I430" s="6" t="s">
@@ -22209,7 +22215,7 @@
       <c r="G431" s="5" t="s">
         <v>1661</v>
       </c>
-      <c r="H431" s="10">
+      <c r="H431" s="8">
         <v>6.68</v>
       </c>
       <c r="I431" s="6" t="s">
@@ -22238,7 +22244,7 @@
       <c r="G432" s="5" t="s">
         <v>1668</v>
       </c>
-      <c r="H432" s="10">
+      <c r="H432" s="8">
         <v>9.18</v>
       </c>
       <c r="I432" s="6" t="s">
@@ -22267,7 +22273,7 @@
       <c r="G433" s="5" t="s">
         <v>1675</v>
       </c>
-      <c r="H433" s="10">
+      <c r="H433" s="8">
         <v>4.18</v>
       </c>
       <c r="I433" s="6" t="s">
@@ -22296,7 +22302,7 @@
       <c r="G434" s="5" t="s">
         <v>1675</v>
       </c>
-      <c r="H434" s="10">
+      <c r="H434" s="8">
         <v>8.43</v>
       </c>
       <c r="I434" s="6" t="s">
@@ -22323,7 +22329,7 @@
       <c r="G435" s="5" t="s">
         <v>1675</v>
       </c>
-      <c r="H435" s="10">
+      <c r="H435" s="8">
         <v>8.43</v>
       </c>
       <c r="I435" s="6" t="s">
@@ -22350,7 +22356,7 @@
       <c r="G436" s="5" t="s">
         <v>1686</v>
       </c>
-      <c r="H436" s="10">
+      <c r="H436" s="8">
         <v>47.99</v>
       </c>
       <c r="I436" s="6" t="s">
@@ -22379,7 +22385,7 @@
       <c r="G437" s="5" t="s">
         <v>1692</v>
       </c>
-      <c r="H437" s="10">
+      <c r="H437" s="8">
         <v>23.2</v>
       </c>
       <c r="I437" s="6" t="s">
@@ -22408,7 +22414,7 @@
       <c r="G438" s="5" t="s">
         <v>1697</v>
       </c>
-      <c r="H438" s="10">
+      <c r="H438" s="8">
         <v>2.74</v>
       </c>
       <c r="I438" s="6" t="s">
@@ -22437,7 +22443,7 @@
       <c r="G439" s="5" t="s">
         <v>1697</v>
       </c>
-      <c r="H439" s="10">
+      <c r="H439" s="8">
         <v>2.74</v>
       </c>
       <c r="I439" s="6" t="s">
@@ -22464,7 +22470,7 @@
       <c r="G440" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H440" s="10">
+      <c r="H440" s="8">
         <v>6.33</v>
       </c>
       <c r="I440" s="6" t="s">
@@ -22491,7 +22497,7 @@
       <c r="G441" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H441" s="10">
+      <c r="H441" s="8">
         <v>6.33</v>
       </c>
       <c r="I441" s="6" t="s">
@@ -22520,7 +22526,7 @@
       <c r="G442" s="5" t="s">
         <v>1707</v>
       </c>
-      <c r="H442" s="10">
+      <c r="H442" s="8">
         <v>31.64</v>
       </c>
       <c r="I442" s="6" t="s">
@@ -22547,7 +22553,7 @@
       <c r="G443" s="5" t="s">
         <v>1707</v>
       </c>
-      <c r="H443" s="10">
+      <c r="H443" s="8">
         <v>31.64</v>
       </c>
       <c r="I443" s="6" t="s">
@@ -22574,7 +22580,7 @@
       <c r="G444" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H444" s="10">
+      <c r="H444" s="8">
         <v>5.17</v>
       </c>
       <c r="I444" s="6" t="s">
@@ -22601,7 +22607,7 @@
       <c r="G445" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H445" s="10">
+      <c r="H445" s="8">
         <v>5.17</v>
       </c>
       <c r="I445" s="6" t="s">
@@ -22630,7 +22636,7 @@
       <c r="G446" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H446" s="10">
+      <c r="H446" s="8">
         <v>5.42</v>
       </c>
       <c r="I446" s="6" t="s">
@@ -22657,7 +22663,7 @@
       <c r="G447" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H447" s="10">
+      <c r="H447" s="8">
         <v>10.01</v>
       </c>
       <c r="I447" s="6" t="s">
@@ -22684,7 +22690,7 @@
       <c r="G448" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H448" s="10">
+      <c r="H448" s="8">
         <v>10.01</v>
       </c>
       <c r="I448" s="6" t="s">
@@ -22713,7 +22719,7 @@
       <c r="G449" s="5" t="s">
         <v>1724</v>
       </c>
-      <c r="H449" s="10">
+      <c r="H449" s="8">
         <v>80.66</v>
       </c>
       <c r="I449" s="6" t="s">
@@ -22740,7 +22746,7 @@
       <c r="G450" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H450" s="10">
+      <c r="H450" s="8">
         <v>5.0599999999999996</v>
       </c>
       <c r="I450" s="6" t="s">
@@ -22767,7 +22773,7 @@
       <c r="G451" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H451" s="10">
+      <c r="H451" s="8">
         <v>5.0599999999999996</v>
       </c>
       <c r="I451" s="6" t="s">
@@ -22796,7 +22802,7 @@
       <c r="G452" s="5" t="s">
         <v>1730</v>
       </c>
-      <c r="H452" s="10">
+      <c r="H452" s="8">
         <v>64.34</v>
       </c>
       <c r="I452" s="6" t="s">
@@ -22823,7 +22829,7 @@
       <c r="G453" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H453" s="10">
+      <c r="H453" s="8">
         <v>7.84</v>
       </c>
       <c r="I453" s="6" t="s">
@@ -22850,7 +22856,7 @@
       <c r="G454" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H454" s="10">
+      <c r="H454" s="8">
         <v>7.84</v>
       </c>
       <c r="I454" s="6" t="s">
@@ -22879,7 +22885,7 @@
       <c r="G455" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H455" s="10">
+      <c r="H455" s="8">
         <v>388</v>
       </c>
       <c r="I455" s="6" t="s">
@@ -22908,7 +22914,7 @@
       <c r="G456" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H456" s="10">
+      <c r="H456" s="8">
         <v>388</v>
       </c>
       <c r="I456" s="6" t="s">
@@ -22937,7 +22943,7 @@
       <c r="G457" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H457" s="10">
+      <c r="H457" s="8">
         <v>659.6</v>
       </c>
       <c r="I457" s="6" t="s">
@@ -22966,7 +22972,7 @@
       <c r="G458" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H458" s="10">
+      <c r="H458" s="8">
         <v>659.6</v>
       </c>
       <c r="I458" s="6" t="s">
@@ -22995,7 +23001,7 @@
       <c r="G459" s="5" t="s">
         <v>1730</v>
       </c>
-      <c r="H459" s="10">
+      <c r="H459" s="8">
         <v>139</v>
       </c>
       <c r="I459" s="6" t="s">
@@ -23024,7 +23030,7 @@
       <c r="G460" s="5" t="s">
         <v>1756</v>
       </c>
-      <c r="H460" s="10">
+      <c r="H460" s="8">
         <v>48.83</v>
       </c>
       <c r="I460" s="6" t="s">
@@ -23053,7 +23059,7 @@
       <c r="G461" s="5" t="s">
         <v>1756</v>
       </c>
-      <c r="H461" s="10">
+      <c r="H461" s="8">
         <v>48.83</v>
       </c>
       <c r="I461" s="6" t="s">
@@ -23082,7 +23088,7 @@
       <c r="G462" s="5" t="s">
         <v>1761</v>
       </c>
-      <c r="H462" s="10">
+      <c r="H462" s="8">
         <v>10.9</v>
       </c>
       <c r="I462" s="6" t="s">
@@ -23111,7 +23117,7 @@
       <c r="G463" s="5" t="s">
         <v>1761</v>
       </c>
-      <c r="H463" s="10">
+      <c r="H463" s="8">
         <v>10.9</v>
       </c>
       <c r="I463" s="6" t="s">
@@ -23140,7 +23146,7 @@
       <c r="G464" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H464" s="10">
+      <c r="H464" s="8">
         <v>6.21</v>
       </c>
       <c r="I464" s="6" t="s">
@@ -23169,7 +23175,7 @@
       <c r="G465" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H465" s="10">
+      <c r="H465" s="8">
         <v>6.21</v>
       </c>
       <c r="I465" s="6" t="s">
@@ -23196,7 +23202,7 @@
       <c r="G466" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H466" s="10">
+      <c r="H466" s="8">
         <v>59.3</v>
       </c>
       <c r="I466" s="6" t="s">
@@ -23223,7 +23229,7 @@
       <c r="G467" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H467" s="10">
+      <c r="H467" s="8">
         <v>59.3</v>
       </c>
       <c r="I467" s="6" t="s">
@@ -23250,7 +23256,7 @@
       <c r="G468" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H468" s="10">
+      <c r="H468" s="8">
         <v>41.42</v>
       </c>
       <c r="I468" s="6" t="s">
@@ -23277,7 +23283,7 @@
       <c r="G469" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H469" s="10">
+      <c r="H469" s="8">
         <v>41.42</v>
       </c>
       <c r="I469" s="6" t="s">
@@ -23306,7 +23312,7 @@
       <c r="G470" s="5" t="s">
         <v>1781</v>
       </c>
-      <c r="H470" s="10">
+      <c r="H470" s="8">
         <v>38.42</v>
       </c>
       <c r="I470" s="6" t="s">
@@ -23335,7 +23341,7 @@
       <c r="G471" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H471" s="10">
+      <c r="H471" s="8">
         <v>35.549999999999997</v>
       </c>
       <c r="I471" s="6" t="s">
@@ -23364,7 +23370,7 @@
       <c r="G472" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H472" s="10">
+      <c r="H472" s="8">
         <v>35.549999999999997</v>
       </c>
       <c r="I472" s="6" t="s">
@@ -23393,7 +23399,7 @@
       <c r="G473" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="H473" s="10">
+      <c r="H473" s="8">
         <v>25.9</v>
       </c>
       <c r="I473" s="6" t="s">
@@ -23422,7 +23428,7 @@
       <c r="G474" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="H474" s="10">
+      <c r="H474" s="8">
         <v>25.9</v>
       </c>
       <c r="I474" s="6" t="s">
@@ -23451,7 +23457,7 @@
       <c r="G475" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H475" s="10">
+      <c r="H475" s="8">
         <v>29.56</v>
       </c>
       <c r="I475" s="6" t="s">
@@ -23480,7 +23486,7 @@
       <c r="G476" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H476" s="10">
+      <c r="H476" s="8">
         <v>29.56</v>
       </c>
       <c r="I476" s="6" t="s">
@@ -23509,7 +23515,7 @@
       <c r="G477" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H477" s="10">
+      <c r="H477" s="8">
         <v>80.11</v>
       </c>
       <c r="I477" s="6" t="s">
@@ -23538,7 +23544,7 @@
       <c r="G478" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H478" s="10">
+      <c r="H478" s="8">
         <v>80.11</v>
       </c>
       <c r="I478" s="6" t="s">
@@ -23567,7 +23573,7 @@
       <c r="G479" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H479" s="10">
+      <c r="H479" s="8">
         <v>89.91</v>
       </c>
       <c r="I479" s="6" t="s">
@@ -23596,7 +23602,7 @@
       <c r="G480" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H480" s="10">
+      <c r="H480" s="8">
         <v>89.91</v>
       </c>
       <c r="I480" s="6" t="s">
@@ -23625,7 +23631,7 @@
       <c r="G481" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="H481" s="10">
+      <c r="H481" s="8">
         <v>65.3</v>
       </c>
       <c r="I481" s="6" t="s">
@@ -23654,7 +23660,7 @@
       <c r="G482" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="H482" s="10">
+      <c r="H482" s="8">
         <v>65.3</v>
       </c>
       <c r="I482" s="6" t="s">
@@ -23683,7 +23689,7 @@
       <c r="G483" s="5" t="s">
         <v>1618</v>
       </c>
-      <c r="H483" s="10">
+      <c r="H483" s="8">
         <v>279</v>
       </c>
       <c r="I483" s="6" t="s">
@@ -23712,7 +23718,7 @@
       <c r="G484" s="5" t="s">
         <v>1781</v>
       </c>
-      <c r="H484" s="10">
+      <c r="H484" s="8">
         <v>38.42</v>
       </c>
       <c r="I484" s="6" t="s">
@@ -23741,7 +23747,7 @@
       <c r="G485" s="5" t="s">
         <v>1781</v>
       </c>
-      <c r="H485" s="10">
+      <c r="H485" s="8">
         <v>38.42</v>
       </c>
       <c r="I485" s="6" t="s">
@@ -23770,7 +23776,7 @@
       <c r="G486" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H486" s="10">
+      <c r="H486" s="8">
         <v>35.549999999999997</v>
       </c>
       <c r="I486" s="6" t="s">
@@ -23799,7 +23805,7 @@
       <c r="G487" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H487" s="10">
+      <c r="H487" s="8">
         <v>35.549999999999997</v>
       </c>
       <c r="I487" s="6" t="s">
@@ -23828,7 +23834,7 @@
       <c r="G488" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="H488" s="10">
+      <c r="H488" s="8">
         <v>25.9</v>
       </c>
       <c r="I488" s="6" t="s">
@@ -23857,7 +23863,7 @@
       <c r="G489" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H489" s="10">
+      <c r="H489" s="8">
         <v>74.36</v>
       </c>
       <c r="I489" s="6" t="s">
@@ -23886,7 +23892,7 @@
       <c r="G490" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H490" s="10">
+      <c r="H490" s="8">
         <v>74.36</v>
       </c>
       <c r="I490" s="6" t="s">
@@ -23913,7 +23919,7 @@
       <c r="G491" s="5" t="s">
         <v>1852</v>
       </c>
-      <c r="H491" s="10">
+      <c r="H491" s="8">
         <v>8.31</v>
       </c>
       <c r="I491" s="6" t="s">
@@ -23942,7 +23948,7 @@
       <c r="G492" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H492" s="10">
+      <c r="H492" s="8">
         <v>226.58</v>
       </c>
       <c r="I492" s="6" t="s">
@@ -23971,7 +23977,7 @@
       <c r="G493" s="5" t="s">
         <v>1381</v>
       </c>
-      <c r="H493" s="10">
+      <c r="H493" s="8">
         <v>226.58</v>
       </c>
       <c r="I493" s="6" t="s">
@@ -24000,7 +24006,7 @@
       <c r="G494" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H494" s="10">
+      <c r="H494" s="8">
         <v>217.6</v>
       </c>
       <c r="I494" s="6" t="s">
@@ -24029,7 +24035,7 @@
       <c r="G495" s="5" t="s">
         <v>1741</v>
       </c>
-      <c r="H495" s="10">
+      <c r="H495" s="8">
         <v>217.6</v>
       </c>
       <c r="I495" s="6" t="s">
@@ -24058,7 +24064,7 @@
       <c r="G496" s="5" t="s">
         <v>1870</v>
       </c>
-      <c r="H496" s="10">
+      <c r="H496" s="8">
         <v>24.88</v>
       </c>
       <c r="I496" s="6" t="s">
@@ -24087,7 +24093,7 @@
       <c r="G497" s="5" t="s">
         <v>1870</v>
       </c>
-      <c r="H497" s="10">
+      <c r="H497" s="8">
         <v>24.88</v>
       </c>
       <c r="I497" s="6" t="s">
@@ -24116,7 +24122,7 @@
       <c r="G498" s="5" t="s">
         <v>1876</v>
       </c>
-      <c r="H498" s="10">
+      <c r="H498" s="8">
         <v>26.6</v>
       </c>
       <c r="I498" s="6" t="s">
@@ -24145,7 +24151,7 @@
       <c r="G499" s="5" t="s">
         <v>1876</v>
       </c>
-      <c r="H499" s="10">
+      <c r="H499" s="8">
         <v>26.6</v>
       </c>
       <c r="I499" s="6" t="s">
@@ -24172,7 +24178,7 @@
       <c r="G500" s="5" t="s">
         <v>1882</v>
       </c>
-      <c r="H500" s="10">
+      <c r="H500" s="8">
         <v>2.4300000000000002</v>
       </c>
       <c r="I500" s="6" t="s">
@@ -24201,7 +24207,7 @@
       <c r="G501" s="5" t="s">
         <v>1886</v>
       </c>
-      <c r="H501" s="10">
+      <c r="H501" s="8">
         <v>4.8</v>
       </c>
       <c r="I501" s="6" t="s">
@@ -24230,7 +24236,7 @@
       <c r="G502" s="5" t="s">
         <v>1886</v>
       </c>
-      <c r="H502" s="10">
+      <c r="H502" s="8">
         <v>4.8</v>
       </c>
       <c r="I502" s="6" t="s">
@@ -24257,7 +24263,7 @@
       <c r="G503" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H503" s="10">
+      <c r="H503" s="8">
         <v>4.96</v>
       </c>
       <c r="I503" s="6" t="s">
@@ -24286,7 +24292,7 @@
       <c r="G504" s="5" t="s">
         <v>1899</v>
       </c>
-      <c r="H504" s="10">
+      <c r="H504" s="8">
         <v>7.48</v>
       </c>
       <c r="I504" s="6" t="s">
@@ -24315,7 +24321,7 @@
       <c r="G505" s="5" t="s">
         <v>1905</v>
       </c>
-      <c r="H505" s="10">
+      <c r="H505" s="8">
         <v>0.23</v>
       </c>
       <c r="I505" s="6" t="s">
@@ -24344,7 +24350,7 @@
       <c r="G506" s="5" t="s">
         <v>1905</v>
       </c>
-      <c r="H506" s="10">
+      <c r="H506" s="8">
         <v>0.23</v>
       </c>
       <c r="I506" s="6" t="s">
@@ -24371,7 +24377,7 @@
       <c r="G507" s="5" t="s">
         <v>1911</v>
       </c>
-      <c r="H507" s="10">
+      <c r="H507" s="8">
         <v>24.43</v>
       </c>
       <c r="I507" s="6" t="s">
@@ -24400,7 +24406,7 @@
       <c r="G508" s="5" t="s">
         <v>1915</v>
       </c>
-      <c r="H508" s="10">
+      <c r="H508" s="8">
         <v>19.309999999999999</v>
       </c>
       <c r="I508" s="6" t="s">
@@ -24429,7 +24435,7 @@
       <c r="G509" s="5" t="s">
         <v>1915</v>
       </c>
-      <c r="H509" s="10">
+      <c r="H509" s="8">
         <v>19.309999999999999</v>
       </c>
       <c r="I509" s="6" t="s">
@@ -24456,7 +24462,7 @@
       <c r="G510" s="5" t="s">
         <v>1920</v>
       </c>
-      <c r="H510" s="10">
+      <c r="H510" s="8">
         <v>3.29</v>
       </c>
       <c r="I510" s="6" t="s">
@@ -24483,7 +24489,7 @@
       <c r="G511" s="5" t="s">
         <v>1920</v>
       </c>
-      <c r="H511" s="10">
+      <c r="H511" s="8">
         <v>3.29</v>
       </c>
       <c r="I511" s="6" t="s">
@@ -24510,7 +24516,7 @@
       <c r="G512" s="5" t="s">
         <v>1927</v>
       </c>
-      <c r="H512" s="10">
+      <c r="H512" s="8">
         <v>85.82</v>
       </c>
       <c r="I512" s="6" t="s">
@@ -24537,7 +24543,7 @@
       <c r="G513" s="5" t="s">
         <v>1596</v>
       </c>
-      <c r="H513" s="10">
+      <c r="H513" s="8">
         <v>41.36</v>
       </c>
       <c r="I513" s="6" t="s">
@@ -24564,7 +24570,7 @@
       <c r="G514" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H514" s="10">
+      <c r="H514" s="8">
         <v>3.9</v>
       </c>
       <c r="I514" s="6" t="s">
@@ -24591,7 +24597,7 @@
       <c r="G515" s="5" t="s">
         <v>1941</v>
       </c>
-      <c r="H515" s="10">
+      <c r="H515" s="8">
         <v>60.54</v>
       </c>
       <c r="I515" s="6" t="s">
@@ -24620,7 +24626,7 @@
       <c r="G516" s="5" t="s">
         <v>1948</v>
       </c>
-      <c r="H516" s="10">
+      <c r="H516" s="8">
         <v>520</v>
       </c>
       <c r="I516" s="6" t="s">
@@ -24647,7 +24653,7 @@
       <c r="G517" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H517" s="10">
+      <c r="H517" s="8">
         <v>22.8</v>
       </c>
       <c r="I517" s="6" t="s">
@@ -24676,7 +24682,7 @@
       <c r="G518" s="5" t="s">
         <v>1957</v>
       </c>
-      <c r="H518" s="10">
+      <c r="H518" s="8">
         <v>95.25</v>
       </c>
       <c r="I518" s="6" t="s">
@@ -24703,7 +24709,7 @@
       <c r="G519" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H519" s="10">
+      <c r="H519" s="8">
         <v>1.8</v>
       </c>
       <c r="I519" s="6" t="s">
@@ -24730,7 +24736,7 @@
       <c r="G520" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H520" s="10">
+      <c r="H520" s="8">
         <v>1153</v>
       </c>
       <c r="I520" s="6" t="s">
@@ -24759,7 +24765,7 @@
       <c r="G521" s="5" t="s">
         <v>1970</v>
       </c>
-      <c r="H521" s="10">
+      <c r="H521" s="8">
         <v>428</v>
       </c>
       <c r="I521" s="6" t="s">
@@ -24786,7 +24792,7 @@
       <c r="G522" s="5" t="s">
         <v>1973</v>
       </c>
-      <c r="H522" s="10">
+      <c r="H522" s="8">
         <v>16.8</v>
       </c>
       <c r="I522" s="6" t="s">
@@ -24813,7 +24819,7 @@
       <c r="G523" s="5" t="s">
         <v>1978</v>
       </c>
-      <c r="H523" s="10">
+      <c r="H523" s="8">
         <v>31.82</v>
       </c>
       <c r="I523" s="6" t="s">
@@ -24842,7 +24848,7 @@
       <c r="G524" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H524" s="10">
+      <c r="H524" s="8">
         <v>10.8</v>
       </c>
       <c r="I524" s="6" t="s">
@@ -24871,7 +24877,7 @@
       <c r="G525" s="5" t="s">
         <v>1989</v>
       </c>
-      <c r="H525" s="10">
+      <c r="H525" s="8">
         <v>26</v>
       </c>
       <c r="I525" s="6" t="s">
@@ -24900,7 +24906,7 @@
       <c r="G526" s="5" t="s">
         <v>1996</v>
       </c>
-      <c r="H526" s="10">
+      <c r="H526" s="8">
         <v>59.6</v>
       </c>
       <c r="I526" s="6" t="s">
@@ -24929,7 +24935,7 @@
       <c r="G527" s="5" t="s">
         <v>1970</v>
       </c>
-      <c r="H527" s="10">
+      <c r="H527" s="8">
         <v>153</v>
       </c>
       <c r="I527" s="6" t="s">
@@ -24958,7 +24964,7 @@
       <c r="G528" s="5" t="s">
         <v>2007</v>
       </c>
-      <c r="H528" s="10">
+      <c r="H528" s="8">
         <v>90</v>
       </c>
       <c r="I528" s="6" t="s">
@@ -24987,7 +24993,7 @@
       <c r="G529" s="5" t="s">
         <v>2013</v>
       </c>
-      <c r="H529" s="10">
+      <c r="H529" s="8">
         <v>4.8</v>
       </c>
       <c r="I529" s="6" t="s">
@@ -25016,7 +25022,7 @@
       <c r="G530" s="5" t="s">
         <v>2013</v>
       </c>
-      <c r="H530" s="10">
+      <c r="H530" s="8">
         <v>4.8</v>
       </c>
       <c r="I530" s="6" t="s">
@@ -25043,7 +25049,7 @@
       <c r="G531" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="H531" s="10">
+      <c r="H531" s="8">
         <v>5.99</v>
       </c>
       <c r="I531" s="6" t="s">
@@ -25072,7 +25078,7 @@
       <c r="G532" s="5" t="s">
         <v>2023</v>
       </c>
-      <c r="H532" s="10">
+      <c r="H532" s="8">
         <v>10.39</v>
       </c>
       <c r="I532" s="6" t="s">
@@ -25101,7 +25107,7 @@
       <c r="G533" s="5" t="s">
         <v>2023</v>
       </c>
-      <c r="H533" s="10">
+      <c r="H533" s="8">
         <v>10.39</v>
       </c>
       <c r="I533" s="6" t="s">
@@ -25128,7 +25134,7 @@
       <c r="G534" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H534" s="10">
+      <c r="H534" s="8">
         <v>15.6</v>
       </c>
       <c r="I534" s="6" t="s">
@@ -25155,7 +25161,7 @@
       <c r="G535" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H535" s="10">
+      <c r="H535" s="8">
         <v>15.6</v>
       </c>
       <c r="I535" s="6" t="s">
@@ -25184,7 +25190,7 @@
       <c r="G536" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H536" s="10">
+      <c r="H536" s="8">
         <v>27.54</v>
       </c>
       <c r="I536" s="6" t="s">
@@ -25211,7 +25217,7 @@
       <c r="G537" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="H537" s="10">
+      <c r="H537" s="8">
         <v>14.61</v>
       </c>
       <c r="I537" s="6" t="s">
@@ -25238,7 +25244,7 @@
       <c r="G538" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="H538" s="10">
+      <c r="H538" s="8">
         <v>14.61</v>
       </c>
       <c r="I538" s="6" t="s">
@@ -25265,7 +25271,7 @@
       <c r="G539" s="5" t="s">
         <v>2044</v>
       </c>
-      <c r="H539" s="10">
+      <c r="H539" s="8">
         <v>43.8</v>
       </c>
       <c r="I539" s="6" t="s">
@@ -25294,7 +25300,7 @@
       <c r="G540" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="H540" s="10">
+      <c r="H540" s="8">
         <v>56.33</v>
       </c>
       <c r="I540" s="6" t="s">
@@ -25323,7 +25329,7 @@
       <c r="G541" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="H541" s="10">
+      <c r="H541" s="8">
         <v>56.33</v>
       </c>
       <c r="I541" s="6" t="s">
@@ -25352,7 +25358,7 @@
       <c r="G542" s="5" t="s">
         <v>2056</v>
       </c>
-      <c r="H542" s="10">
+      <c r="H542" s="8">
         <v>64.88</v>
       </c>
       <c r="I542" s="6" t="s">
@@ -25381,7 +25387,7 @@
       <c r="G543" s="5" t="s">
         <v>2056</v>
       </c>
-      <c r="H543" s="10">
+      <c r="H543" s="8">
         <v>64.88</v>
       </c>
       <c r="I543" s="6" t="s">
@@ -25406,7 +25412,7 @@
       <c r="G544" s="5" t="s">
         <v>2061</v>
       </c>
-      <c r="H544" s="10">
+      <c r="H544" s="8">
         <v>17.170000000000002</v>
       </c>
       <c r="I544" s="6" t="s">
@@ -25435,7 +25441,7 @@
       <c r="G545" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H545" s="10">
+      <c r="H545" s="8">
         <v>18.7</v>
       </c>
       <c r="I545" s="6" t="s">
@@ -25464,7 +25470,7 @@
       <c r="G546" s="5" t="s">
         <v>1187</v>
       </c>
-      <c r="H546" s="10">
+      <c r="H546" s="8">
         <v>28.94</v>
       </c>
       <c r="I546" s="6" t="s">
@@ -25493,7 +25499,7 @@
       <c r="G547" s="5" t="s">
         <v>2076</v>
       </c>
-      <c r="H547" s="10">
+      <c r="H547" s="8">
         <v>14.19</v>
       </c>
       <c r="I547" s="6" t="s">
@@ -25522,7 +25528,7 @@
       <c r="G548" s="5" t="s">
         <v>2076</v>
       </c>
-      <c r="H548" s="10">
+      <c r="H548" s="8">
         <v>14.19</v>
       </c>
       <c r="I548" s="6" t="s">
@@ -25549,7 +25555,7 @@
       <c r="G549" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H549" s="10">
+      <c r="H549" s="8">
         <v>6.2</v>
       </c>
       <c r="I549" s="6" t="s">
@@ -25576,7 +25582,7 @@
       <c r="G550" s="5" t="s">
         <v>2086</v>
       </c>
-      <c r="H550" s="10">
+      <c r="H550" s="8">
         <v>61.67</v>
       </c>
       <c r="I550" s="6" t="s">
@@ -25605,7 +25611,7 @@
       <c r="G551" s="5" t="s">
         <v>2092</v>
       </c>
-      <c r="H551" s="10">
+      <c r="H551" s="8">
         <v>19.88</v>
       </c>
       <c r="I551" s="6" t="s">
@@ -25634,7 +25640,7 @@
       <c r="G552" s="5" t="s">
         <v>2092</v>
       </c>
-      <c r="H552" s="10">
+      <c r="H552" s="8">
         <v>19.88</v>
       </c>
       <c r="I552" s="6" t="s">
@@ -25661,7 +25667,7 @@
       <c r="G553" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="H553" s="10">
+      <c r="H553" s="8">
         <v>18.21</v>
       </c>
       <c r="I553" s="6" t="s">
@@ -25688,7 +25694,7 @@
       <c r="G554" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="H554" s="10">
+      <c r="H554" s="8">
         <v>18.21</v>
       </c>
       <c r="I554" s="6" t="s">
@@ -25715,7 +25721,7 @@
       <c r="G555" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H555" s="10">
+      <c r="H555" s="8">
         <v>14.73</v>
       </c>
       <c r="I555" s="6" t="s">
@@ -25744,7 +25750,7 @@
       <c r="G556" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H556" s="10">
+      <c r="H556" s="8">
         <v>84</v>
       </c>
       <c r="I556" s="6" t="s">
@@ -25773,7 +25779,7 @@
       <c r="G557" s="5" t="s">
         <v>2116</v>
       </c>
-      <c r="H557" s="10">
+      <c r="H557" s="8">
         <v>38.15</v>
       </c>
       <c r="I557" s="6" t="s">
@@ -25800,7 +25806,7 @@
       <c r="G558" s="5" t="s">
         <v>2121</v>
       </c>
-      <c r="H558" s="10">
+      <c r="H558" s="8">
         <v>31.87</v>
       </c>
       <c r="I558" s="6" t="s">
@@ -25827,7 +25833,7 @@
       <c r="G559" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H559" s="10">
+      <c r="H559" s="8">
         <v>2.74</v>
       </c>
       <c r="I559" s="6" t="s">
@@ -25854,7 +25860,7 @@
       <c r="G560" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H560" s="10">
+      <c r="H560" s="8">
         <v>2.74</v>
       </c>
       <c r="I560" s="6" t="s">
@@ -25881,7 +25887,7 @@
       <c r="G561" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H561" s="10">
+      <c r="H561" s="8">
         <v>3</v>
       </c>
       <c r="I561" s="6" t="s">
@@ -25908,7 +25914,7 @@
       <c r="G562" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H562" s="10">
+      <c r="H562" s="8">
         <v>3</v>
       </c>
       <c r="I562" s="6" t="s">
@@ -25935,7 +25941,7 @@
       <c r="G563" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H563" s="10">
+      <c r="H563" s="8">
         <v>3.33</v>
       </c>
       <c r="I563" s="6" t="s">
@@ -25962,7 +25968,7 @@
       <c r="G564" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H564" s="10">
+      <c r="H564" s="8">
         <v>3.33</v>
       </c>
       <c r="I564" s="6" t="s">
@@ -25991,7 +25997,7 @@
       <c r="G565" s="5" t="s">
         <v>1504</v>
       </c>
-      <c r="H565" s="10">
+      <c r="H565" s="8">
         <v>10.72</v>
       </c>
       <c r="I565" s="6" t="s">
@@ -26018,7 +26024,7 @@
       <c r="G566" s="5" t="s">
         <v>2149</v>
       </c>
-      <c r="H566" s="10">
+      <c r="H566" s="8">
         <v>28.2</v>
       </c>
       <c r="I566" s="6" t="s">
@@ -26047,7 +26053,7 @@
       <c r="G567" s="5" t="s">
         <v>2154</v>
       </c>
-      <c r="H567" s="10">
+      <c r="H567" s="8">
         <v>10.9</v>
       </c>
       <c r="I567" s="6" t="s">
@@ -26076,7 +26082,7 @@
       <c r="G568" s="5" t="s">
         <v>2154</v>
       </c>
-      <c r="H568" s="10">
+      <c r="H568" s="8">
         <v>10.9</v>
       </c>
       <c r="I568" s="6" t="s">
@@ -26103,7 +26109,7 @@
       <c r="G569" s="5" t="s">
         <v>2159</v>
       </c>
-      <c r="H569" s="10">
+      <c r="H569" s="8">
         <v>1</v>
       </c>
       <c r="I569" s="6" t="s">
@@ -26130,7 +26136,7 @@
       <c r="G570" s="5" t="s">
         <v>2159</v>
       </c>
-      <c r="H570" s="10">
+      <c r="H570" s="8">
         <v>1</v>
       </c>
       <c r="I570" s="6" t="s">
@@ -26157,7 +26163,7 @@
       <c r="G571" s="5" t="s">
         <v>2166</v>
       </c>
-      <c r="H571" s="10">
+      <c r="H571" s="8">
         <v>0.35</v>
       </c>
       <c r="I571" s="6" t="s">
@@ -26186,7 +26192,7 @@
       <c r="G572" s="5" t="s">
         <v>2173</v>
       </c>
-      <c r="H572" s="10">
+      <c r="H572" s="8">
         <v>77.489999999999995</v>
       </c>
       <c r="I572" s="6" t="s">
@@ -26215,7 +26221,7 @@
       <c r="G573" s="5" t="s">
         <v>2173</v>
       </c>
-      <c r="H573" s="10">
+      <c r="H573" s="8">
         <v>77.489999999999995</v>
       </c>
       <c r="I573" s="6" t="s">
@@ -26242,7 +26248,7 @@
       <c r="G574" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="H574" s="10">
+      <c r="H574" s="8">
         <v>0.67</v>
       </c>
       <c r="I574" s="6" t="s">
@@ -26269,7 +26275,7 @@
       <c r="G575" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="H575" s="10">
+      <c r="H575" s="8">
         <v>0.99</v>
       </c>
       <c r="I575" s="6" t="s">
@@ -26296,7 +26302,7 @@
       <c r="G576" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="H576" s="10">
+      <c r="H576" s="8">
         <v>8.2100000000000009</v>
       </c>
       <c r="I576" s="6" t="s">
@@ -26323,7 +26329,7 @@
       <c r="G577" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H577" s="10">
+      <c r="H577" s="8">
         <v>2.2999999999999998</v>
       </c>
       <c r="I577" s="6" t="s">
@@ -26350,7 +26356,7 @@
       <c r="G578" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="H578" s="10">
+      <c r="H578" s="8">
         <v>2.2999999999999998</v>
       </c>
       <c r="I578" s="6" t="s">
@@ -26379,7 +26385,7 @@
       <c r="G579" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="H579" s="10">
+      <c r="H579" s="8">
         <v>0.81</v>
       </c>
       <c r="I579" s="6" t="s">
@@ -26408,7 +26414,7 @@
       <c r="G580" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="H580" s="10">
+      <c r="H580" s="8">
         <v>0.81</v>
       </c>
       <c r="I580" s="6" t="s">
@@ -26435,7 +26441,7 @@
       <c r="G581" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H581" s="10">
+      <c r="H581" s="8">
         <v>18.25</v>
       </c>
       <c r="I581" s="6" t="s">
@@ -26462,7 +26468,7 @@
       <c r="G582" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H582" s="10">
+      <c r="H582" s="8">
         <v>18.25</v>
       </c>
       <c r="I582" s="6" t="s">
@@ -26489,7 +26495,7 @@
       <c r="G583" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H583" s="10">
+      <c r="H583" s="8">
         <v>18.25</v>
       </c>
       <c r="I583" s="6" t="s">
@@ -26516,7 +26522,7 @@
       <c r="G584" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H584" s="10">
+      <c r="H584" s="8">
         <v>33.25</v>
       </c>
       <c r="I584" s="6" t="s">
@@ -26543,7 +26549,7 @@
       <c r="G585" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H585" s="10">
+      <c r="H585" s="8">
         <v>18.25</v>
       </c>
       <c r="I585" s="6" t="s">
@@ -26570,7 +26576,7 @@
       <c r="G586" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H586" s="10">
+      <c r="H586" s="8">
         <v>33.25</v>
       </c>
       <c r="I586" s="6" t="s">
@@ -26599,7 +26605,7 @@
       <c r="G587" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="H587" s="10">
+      <c r="H587" s="8">
         <v>68.5</v>
       </c>
       <c r="I587" s="6" t="s">
@@ -26628,7 +26634,7 @@
       <c r="G588" s="5" t="s">
         <v>2232</v>
       </c>
-      <c r="H588" s="10">
+      <c r="H588" s="8">
         <v>21.29</v>
       </c>
       <c r="I588" s="6" t="s">
@@ -26655,7 +26661,7 @@
       <c r="G589" s="5" t="s">
         <v>2237</v>
       </c>
-      <c r="H589" s="10">
+      <c r="H589" s="8">
         <v>27.88</v>
       </c>
       <c r="I589" s="6" t="s">
@@ -26682,7 +26688,7 @@
       <c r="G590" s="5" t="s">
         <v>2241</v>
       </c>
-      <c r="H590" s="10">
+      <c r="H590" s="8">
         <v>45</v>
       </c>
       <c r="I590" s="6" t="s">
@@ -26709,7 +26715,7 @@
       <c r="G591" s="5" t="s">
         <v>2241</v>
       </c>
-      <c r="H591" s="10">
+      <c r="H591" s="8">
         <v>45</v>
       </c>
       <c r="I591" s="6" t="s">
@@ -26736,7 +26742,7 @@
       <c r="G592" s="5" t="s">
         <v>1438</v>
       </c>
-      <c r="H592" s="10">
+      <c r="H592" s="8">
         <v>99.69</v>
       </c>
       <c r="I592" s="6" t="s">
@@ -26765,7 +26771,7 @@
       <c r="G593" s="5" t="s">
         <v>2252</v>
       </c>
-      <c r="H593" s="10">
+      <c r="H593" s="8">
         <v>6.22</v>
       </c>
       <c r="I593" s="6" t="s">
@@ -26794,7 +26800,7 @@
       <c r="G594" s="5" t="s">
         <v>2252</v>
       </c>
-      <c r="H594" s="10">
+      <c r="H594" s="8">
         <v>6.22</v>
       </c>
       <c r="I594" s="6" t="s">
@@ -26821,7 +26827,7 @@
       <c r="G595" s="5" t="s">
         <v>1423</v>
       </c>
-      <c r="H595" s="10">
+      <c r="H595" s="8">
         <v>3.72</v>
       </c>
       <c r="I595" s="6" t="s">
@@ -26848,7 +26854,7 @@
       <c r="G596" s="5" t="s">
         <v>1423</v>
       </c>
-      <c r="H596" s="10">
+      <c r="H596" s="8">
         <v>3.72</v>
       </c>
       <c r="I596" s="6" t="s">
@@ -26875,7 +26881,7 @@
       <c r="G597" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H597" s="10">
+      <c r="H597" s="8">
         <v>7.18</v>
       </c>
       <c r="I597" s="6" t="s">
@@ -26902,7 +26908,7 @@
       <c r="G598" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H598" s="10">
+      <c r="H598" s="8">
         <v>2.75</v>
       </c>
       <c r="I598" s="6" t="s">
@@ -26929,7 +26935,7 @@
       <c r="G599" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H599" s="10">
+      <c r="H599" s="8">
         <v>2.75</v>
       </c>
       <c r="I599" s="6" t="s">
@@ -26958,7 +26964,7 @@
       <c r="G600" s="5" t="s">
         <v>2274</v>
       </c>
-      <c r="H600" s="10">
+      <c r="H600" s="8">
         <v>30.55</v>
       </c>
       <c r="I600" s="6" t="s">
@@ -26987,7 +26993,7 @@
       <c r="G601" s="5" t="s">
         <v>2274</v>
       </c>
-      <c r="H601" s="10">
+      <c r="H601" s="8">
         <v>30.55</v>
       </c>
       <c r="I601" s="6" t="s">
@@ -27014,7 +27020,7 @@
       <c r="G602" s="5" t="s">
         <v>2279</v>
       </c>
-      <c r="H602" s="10">
+      <c r="H602" s="8">
         <v>10.08</v>
       </c>
       <c r="I602" s="6" t="s">
@@ -27043,7 +27049,7 @@
       <c r="G603" s="5" t="s">
         <v>2286</v>
       </c>
-      <c r="H603" s="10">
+      <c r="H603" s="8">
         <v>185.99</v>
       </c>
       <c r="I603" s="6" t="s">
@@ -27070,7 +27076,7 @@
       <c r="G604" s="5" t="s">
         <v>2290</v>
       </c>
-      <c r="H604" s="10">
+      <c r="H604" s="8">
         <v>19.96</v>
       </c>
       <c r="I604" s="6" t="s">
@@ -27099,7 +27105,7 @@
       <c r="G605" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H605" s="10">
+      <c r="H605" s="8">
         <v>113.13</v>
       </c>
       <c r="I605" s="6" t="s">
@@ -27126,7 +27132,7 @@
       <c r="G606" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H606" s="10">
+      <c r="H606" s="8">
         <v>46</v>
       </c>
       <c r="I606" s="6" t="s">
@@ -27153,7 +27159,7 @@
       <c r="G607" s="5" t="s">
         <v>2305</v>
       </c>
-      <c r="H607" s="10">
+      <c r="H607" s="8">
         <v>136.91999999999999</v>
       </c>
       <c r="I607" s="6" t="s">
@@ -27180,7 +27186,7 @@
       <c r="G608" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H608" s="10">
+      <c r="H608" s="8">
         <v>415</v>
       </c>
       <c r="I608" s="6" t="s">
@@ -27207,7 +27213,7 @@
       <c r="G609" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H609" s="10">
+      <c r="H609" s="8">
         <v>148</v>
       </c>
       <c r="I609" s="6" t="s">
@@ -27234,7 +27240,7 @@
       <c r="G610" s="5" t="s">
         <v>2317</v>
       </c>
-      <c r="H610" s="10">
+      <c r="H610" s="8">
         <v>59.9</v>
       </c>
       <c r="I610" s="6" t="s">
@@ -27263,7 +27269,7 @@
       <c r="G611" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H611" s="10">
+      <c r="H611" s="8">
         <v>293.5</v>
       </c>
       <c r="I611" s="6" t="s">
@@ -27290,7 +27296,7 @@
       <c r="G612" s="5" t="s">
         <v>2325</v>
       </c>
-      <c r="H612" s="10">
+      <c r="H612" s="8">
         <v>25.77</v>
       </c>
       <c r="I612" s="6" t="s">
@@ -27319,7 +27325,7 @@
       <c r="G613" s="5" t="s">
         <v>2331</v>
       </c>
-      <c r="H613" s="10">
+      <c r="H613" s="8">
         <v>178.8</v>
       </c>
       <c r="I613" s="6" t="s">
@@ -27348,7 +27354,7 @@
       <c r="G614" s="5" t="s">
         <v>2337</v>
       </c>
-      <c r="H614" s="10">
+      <c r="H614" s="8">
         <v>1073.75</v>
       </c>
       <c r="I614" s="6" t="s">
@@ -27377,7 +27383,7 @@
       <c r="G615" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="H615" s="10">
+      <c r="H615" s="8">
         <v>2489.7600000000002</v>
       </c>
       <c r="I615" s="6" t="s">
@@ -27404,7 +27410,7 @@
       <c r="G616" s="5" t="s">
         <v>2344</v>
       </c>
-      <c r="H616" s="10">
+      <c r="H616" s="8">
         <v>38.56</v>
       </c>
       <c r="I616" s="6" t="s">
@@ -27429,7 +27435,7 @@
       <c r="G617" s="5" t="s">
         <v>2344</v>
       </c>
-      <c r="H617" s="10">
+      <c r="H617" s="8">
         <v>38.56</v>
       </c>
       <c r="I617" s="6" t="s">
@@ -27458,7 +27464,7 @@
       <c r="G618" s="5" t="s">
         <v>2350</v>
       </c>
-      <c r="H618" s="10">
+      <c r="H618" s="8">
         <v>763.68</v>
       </c>
       <c r="I618" s="6" t="s">
@@ -27487,7 +27493,7 @@
       <c r="G619" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="H619" s="10">
+      <c r="H619" s="8">
         <v>20.69</v>
       </c>
       <c r="I619" s="6" t="s">
@@ -27516,7 +27522,7 @@
       <c r="G620" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H620" s="10">
+      <c r="H620" s="8">
         <v>122.22</v>
       </c>
       <c r="I620" s="6" t="s">
@@ -27543,7 +27549,7 @@
       <c r="G621" s="5" t="s">
         <v>2364</v>
       </c>
-      <c r="H621" s="10">
+      <c r="H621" s="8">
         <v>7795.2</v>
       </c>
       <c r="I621" s="6" t="s">
@@ -27570,7 +27576,7 @@
       <c r="G622" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H622" s="10">
+      <c r="H622" s="8">
         <v>64.5</v>
       </c>
       <c r="I622" s="6" t="s">
@@ -27599,7 +27605,7 @@
       <c r="G623" s="5" t="s">
         <v>2374</v>
       </c>
-      <c r="H623" s="10">
+      <c r="H623" s="8">
         <v>1000</v>
       </c>
       <c r="I623" s="6" t="s">
@@ -27626,7 +27632,7 @@
       <c r="G624" s="5" t="s">
         <v>2378</v>
       </c>
-      <c r="H624" s="10">
+      <c r="H624" s="8">
         <v>750</v>
       </c>
       <c r="I624" s="6" t="s">
@@ -27655,7 +27661,7 @@
       <c r="G625" s="5" t="s">
         <v>2383</v>
       </c>
-      <c r="H625" s="10">
+      <c r="H625" s="8">
         <v>896.98</v>
       </c>
       <c r="I625" s="6" t="s">
@@ -27682,7 +27688,7 @@
       <c r="G626" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="H626" s="10">
+      <c r="H626" s="8">
         <v>623.53</v>
       </c>
       <c r="I626" s="6" t="s">
@@ -27709,7 +27715,7 @@
       <c r="G627" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="H627" s="10">
+      <c r="H627" s="8">
         <v>623.53</v>
       </c>
       <c r="I627" s="6" t="s">
@@ -27738,7 +27744,7 @@
       <c r="G628" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H628" s="10">
+      <c r="H628" s="8">
         <v>191.66</v>
       </c>
       <c r="I628" s="6" t="s">
@@ -27767,7 +27773,7 @@
       <c r="G629" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="H629" s="10">
+      <c r="H629" s="8">
         <v>396.02</v>
       </c>
       <c r="I629" s="6" t="s">
@@ -27796,7 +27802,7 @@
       <c r="G630" s="5" t="s">
         <v>2252</v>
       </c>
-      <c r="H630" s="10">
+      <c r="H630" s="8">
         <v>185.29</v>
       </c>
       <c r="I630" s="6" t="s">
@@ -27825,7 +27831,7 @@
       <c r="G631" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H631" s="10">
+      <c r="H631" s="8">
         <v>603</v>
       </c>
       <c r="I631" s="6" t="s">
@@ -27854,7 +27860,7 @@
       <c r="G632" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H632" s="10">
+      <c r="H632" s="8">
         <v>1025.0999999999999</v>
       </c>
       <c r="I632" s="6" t="s">
@@ -27883,7 +27889,7 @@
       <c r="G633" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H633" s="10">
+      <c r="H633" s="8">
         <v>646</v>
       </c>
       <c r="I633" s="6" t="s">
@@ -27912,7 +27918,7 @@
       <c r="G634" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H634" s="10">
+      <c r="H634" s="8">
         <v>380</v>
       </c>
       <c r="I634" s="6" t="s">
@@ -27941,7 +27947,7 @@
       <c r="G635" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H635" s="10">
+      <c r="H635" s="8">
         <v>715.6</v>
       </c>
       <c r="I635" s="6" t="s">
@@ -27970,7 +27976,7 @@
       <c r="G636" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="H636" s="10">
+      <c r="H636" s="8">
         <v>420.94</v>
       </c>
       <c r="I636" s="6" t="s">
@@ -27999,7 +28005,7 @@
       <c r="G637" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H637" s="10">
+      <c r="H637" s="8">
         <v>21.18</v>
       </c>
       <c r="I637" s="6" t="s">
@@ -28028,7 +28034,7 @@
       <c r="G638" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="H638" s="10">
+      <c r="H638" s="8">
         <v>45.45</v>
       </c>
       <c r="I638" s="6" t="s">
@@ -28057,7 +28063,7 @@
       <c r="G639" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H639" s="10">
+      <c r="H639" s="8">
         <v>38.24</v>
       </c>
       <c r="I639" s="6" t="s">
@@ -28086,7 +28092,7 @@
       <c r="G640" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H640" s="10">
+      <c r="H640" s="8">
         <v>38.24</v>
       </c>
       <c r="I640" s="6" t="s">
@@ -28115,7 +28121,7 @@
       <c r="G641" s="5" t="s">
         <v>2086</v>
       </c>
-      <c r="H641" s="10">
+      <c r="H641" s="8">
         <v>1285.95</v>
       </c>
       <c r="I641" s="6" t="s">
@@ -28144,7 +28150,7 @@
       <c r="G642" s="5" t="s">
         <v>2446</v>
       </c>
-      <c r="H642" s="10">
+      <c r="H642" s="8">
         <v>179.97</v>
       </c>
       <c r="I642" s="6" t="s">
@@ -28173,7 +28179,7 @@
       <c r="G643" s="5" t="s">
         <v>2446</v>
       </c>
-      <c r="H643" s="10">
+      <c r="H643" s="8">
         <v>179.97</v>
       </c>
       <c r="I643" s="6" t="s">
@@ -28200,7 +28206,7 @@
       <c r="G644" s="5" t="s">
         <v>2452</v>
       </c>
-      <c r="H644" s="10">
+      <c r="H644" s="8">
         <v>34.19</v>
       </c>
       <c r="I644" s="6" t="s">
@@ -28227,7 +28233,7 @@
       <c r="G645" s="5" t="s">
         <v>2455</v>
       </c>
-      <c r="H645" s="10">
+      <c r="H645" s="8">
         <v>32</v>
       </c>
       <c r="I645" s="6" t="s">
@@ -28254,7 +28260,7 @@
       <c r="G646" s="5" t="s">
         <v>2460</v>
       </c>
-      <c r="H646" s="10">
+      <c r="H646" s="8">
         <v>16.27</v>
       </c>
       <c r="I646" s="6" t="s">
@@ -28281,7 +28287,7 @@
       <c r="G647" s="5" t="s">
         <v>2465</v>
       </c>
-      <c r="H647" s="10">
+      <c r="H647" s="8">
         <v>50.38</v>
       </c>
       <c r="I647" s="6" t="s">
@@ -28308,7 +28314,7 @@
       <c r="G648" s="5" t="s">
         <v>2470</v>
       </c>
-      <c r="H648" s="10">
+      <c r="H648" s="8">
         <v>17.2</v>
       </c>
       <c r="I648" s="6" t="s">
@@ -28335,7 +28341,7 @@
       <c r="G649" s="5" t="s">
         <v>2475</v>
       </c>
-      <c r="H649" s="10">
+      <c r="H649" s="8">
         <v>13.9</v>
       </c>
       <c r="I649" s="6" t="s">
@@ -28364,7 +28370,7 @@
       <c r="G650" s="5" t="s">
         <v>2481</v>
       </c>
-      <c r="H650" s="10">
+      <c r="H650" s="8">
         <v>31.65</v>
       </c>
       <c r="I650" s="6" t="s">
@@ -28393,7 +28399,7 @@
       <c r="G651" s="5" t="s">
         <v>2481</v>
       </c>
-      <c r="H651" s="10">
+      <c r="H651" s="8">
         <v>40.049999999999997</v>
       </c>
       <c r="I651" s="6" t="s">
@@ -28422,7 +28428,7 @@
       <c r="G652" s="5" t="s">
         <v>2481</v>
       </c>
-      <c r="H652" s="10">
+      <c r="H652" s="8">
         <v>48.31</v>
       </c>
       <c r="I652" s="6" t="s">
@@ -28451,7 +28457,7 @@
       <c r="G653" s="5" t="s">
         <v>2481</v>
       </c>
-      <c r="H653" s="10">
+      <c r="H653" s="8">
         <v>98.29</v>
       </c>
       <c r="I653" s="6" t="s">
@@ -28480,7 +28486,7 @@
       <c r="G654" s="5" t="s">
         <v>2481</v>
       </c>
-      <c r="H654" s="10">
+      <c r="H654" s="8">
         <v>123.28</v>
       </c>
       <c r="I654" s="6" t="s">
@@ -28507,7 +28513,7 @@
       <c r="G655" s="5" t="s">
         <v>2502</v>
       </c>
-      <c r="H655" s="10">
+      <c r="H655" s="8">
         <v>36</v>
       </c>
       <c r="I655" s="6" t="s">
@@ -28536,7 +28542,7 @@
       <c r="G656" s="5" t="s">
         <v>2508</v>
       </c>
-      <c r="H656" s="10">
+      <c r="H656" s="8">
         <v>1973</v>
       </c>
       <c r="I656" s="6" t="s">
@@ -28565,7 +28571,7 @@
       <c r="G657" s="5" t="s">
         <v>2512</v>
       </c>
-      <c r="H657" s="10">
+      <c r="H657" s="8">
         <v>680</v>
       </c>
       <c r="I657" s="6" t="s">
@@ -28592,7 +28598,7 @@
       <c r="G658" s="5" t="s">
         <v>2516</v>
       </c>
-      <c r="H658" s="10">
+      <c r="H658" s="8">
         <v>76.77</v>
       </c>
       <c r="I658" s="6" t="s">
@@ -28619,7 +28625,7 @@
       <c r="G659" s="5" t="s">
         <v>2516</v>
       </c>
-      <c r="H659" s="10">
+      <c r="H659" s="8">
         <v>76.77</v>
       </c>
       <c r="I659" s="6" t="s">
@@ -28648,7 +28654,7 @@
       <c r="G660" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H660" s="10">
+      <c r="H660" s="8">
         <v>270.2</v>
       </c>
       <c r="I660" s="6" t="s">
@@ -28677,7 +28683,7 @@
       <c r="G661" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H661" s="10">
+      <c r="H661" s="8">
         <v>270.2</v>
       </c>
       <c r="I661" s="6" t="s">
@@ -28704,7 +28710,7 @@
       <c r="G662" s="5" t="s">
         <v>2527</v>
       </c>
-      <c r="H662" s="10">
+      <c r="H662" s="8">
         <v>59.39</v>
       </c>
       <c r="I662" s="6" t="s">
@@ -28731,7 +28737,7 @@
       <c r="G663" s="5" t="s">
         <v>2527</v>
       </c>
-      <c r="H663" s="10">
+      <c r="H663" s="8">
         <v>59.39</v>
       </c>
       <c r="I663" s="6" t="s">
@@ -28760,7 +28766,7 @@
       <c r="G664" s="5" t="s">
         <v>2534</v>
       </c>
-      <c r="H664" s="10">
+      <c r="H664" s="8">
         <v>512.53</v>
       </c>
       <c r="I664" s="6" t="s">
@@ -28787,7 +28793,7 @@
       <c r="G665" s="5" t="s">
         <v>2538</v>
       </c>
-      <c r="H665" s="10">
+      <c r="H665" s="8">
         <v>508</v>
       </c>
       <c r="I665" s="6" t="s">
@@ -28814,7 +28820,7 @@
       <c r="G666" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H666" s="10">
+      <c r="H666" s="8">
         <v>70.5</v>
       </c>
       <c r="I666" s="6" t="s">
@@ -28841,7 +28847,7 @@
       <c r="G667" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H667" s="10">
+      <c r="H667" s="8">
         <v>70.5</v>
       </c>
       <c r="I667" s="6" t="s">
@@ -28868,7 +28874,7 @@
       <c r="G668" s="5" t="s">
         <v>2548</v>
       </c>
-      <c r="H668" s="10">
+      <c r="H668" s="8">
         <v>101.19</v>
       </c>
       <c r="I668" s="6" t="s">
@@ -28897,7 +28903,7 @@
       <c r="G669" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H669" s="10">
+      <c r="H669" s="8">
         <v>20.39</v>
       </c>
       <c r="I669" s="6" t="s">
@@ -28924,7 +28930,7 @@
       <c r="G670" s="5" t="s">
         <v>2558</v>
       </c>
-      <c r="H670" s="10">
+      <c r="H670" s="8">
         <v>5.8</v>
       </c>
       <c r="I670" s="6" t="s">
@@ -28951,7 +28957,7 @@
       <c r="G671" s="5" t="s">
         <v>2558</v>
       </c>
-      <c r="H671" s="10">
+      <c r="H671" s="8">
         <v>5.8</v>
       </c>
       <c r="I671" s="6" t="s">
@@ -28980,7 +28986,7 @@
       <c r="G672" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="H672" s="10">
+      <c r="H672" s="8">
         <v>16.41</v>
       </c>
       <c r="I672" s="6" t="s">
@@ -29009,7 +29015,7 @@
       <c r="G673" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="H673" s="10">
+      <c r="H673" s="8">
         <v>33.409999999999997</v>
       </c>
       <c r="I673" s="6" t="s">
@@ -29038,7 +29044,7 @@
       <c r="G674" s="5" t="s">
         <v>2576</v>
       </c>
-      <c r="H674" s="10">
+      <c r="H674" s="8">
         <v>5.37</v>
       </c>
       <c r="I674" s="6" t="s">
@@ -29067,7 +29073,7 @@
       <c r="G675" s="5" t="s">
         <v>2576</v>
       </c>
-      <c r="H675" s="10">
+      <c r="H675" s="8">
         <v>5.37</v>
       </c>
       <c r="I675" s="6" t="s">
@@ -29096,7 +29102,7 @@
       <c r="G676" s="5" t="s">
         <v>2583</v>
       </c>
-      <c r="H676" s="10">
+      <c r="H676" s="8">
         <v>69.08</v>
       </c>
       <c r="I676" s="6" t="s">
@@ -29123,7 +29129,7 @@
       <c r="G677" s="5" t="s">
         <v>2588</v>
       </c>
-      <c r="H677" s="10">
+      <c r="H677" s="8">
         <v>2.3199999999999998</v>
       </c>
       <c r="I677" s="6" t="s">
@@ -29152,7 +29158,7 @@
       <c r="G678" s="5" t="s">
         <v>2593</v>
       </c>
-      <c r="H678" s="10">
+      <c r="H678" s="8">
         <v>21.14</v>
       </c>
       <c r="I678" s="6" t="s">
@@ -29181,7 +29187,7 @@
       <c r="G679" s="5" t="s">
         <v>2599</v>
       </c>
-      <c r="H679" s="10">
+      <c r="H679" s="8">
         <v>22.08</v>
       </c>
       <c r="I679" s="6" t="s">
@@ -29210,7 +29216,7 @@
       <c r="G680" s="5" t="s">
         <v>2604</v>
       </c>
-      <c r="H680" s="10">
+      <c r="H680" s="8">
         <v>65.13</v>
       </c>
       <c r="I680" s="6" t="s">
@@ -29237,7 +29243,7 @@
       <c r="G681" s="5" t="s">
         <v>2583</v>
       </c>
-      <c r="H681" s="10">
+      <c r="H681" s="8">
         <v>9.75</v>
       </c>
       <c r="I681" s="6" t="s">
@@ -29264,7 +29270,7 @@
       <c r="G682" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="H682" s="10">
+      <c r="H682" s="8">
         <v>21.7</v>
       </c>
       <c r="I682" s="6" t="s">
@@ -29293,7 +29299,7 @@
       <c r="G683" s="5" t="s">
         <v>2616</v>
       </c>
-      <c r="H683" s="10">
+      <c r="H683" s="8">
         <v>74.8</v>
       </c>
       <c r="I683" s="6" t="s">
@@ -29320,7 +29326,7 @@
       <c r="G684" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="H684" s="10">
+      <c r="H684" s="8">
         <v>5</v>
       </c>
       <c r="I684" s="6" t="s">
@@ -29349,7 +29355,7 @@
       <c r="G685" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="H685" s="10">
+      <c r="H685" s="8">
         <v>31.69</v>
       </c>
       <c r="I685" s="6" t="s">
@@ -29376,7 +29382,7 @@
       <c r="G686" s="5" t="s">
         <v>2628</v>
       </c>
-      <c r="H686" s="10">
+      <c r="H686" s="8">
         <v>34.19</v>
       </c>
       <c r="I686" s="6" t="s">
@@ -29405,7 +29411,7 @@
       <c r="G687" s="5" t="s">
         <v>2634</v>
       </c>
-      <c r="H687" s="10">
+      <c r="H687" s="8">
         <v>148.80000000000001</v>
       </c>
       <c r="I687" s="6" t="s">
@@ -29434,7 +29440,7 @@
       <c r="G688" s="5" t="s">
         <v>2616</v>
       </c>
-      <c r="H688" s="10">
+      <c r="H688" s="8">
         <v>33.75</v>
       </c>
       <c r="I688" s="6" t="s">
@@ -29463,7 +29469,7 @@
       <c r="G689" s="5" t="s">
         <v>2644</v>
       </c>
-      <c r="H689" s="10">
+      <c r="H689" s="8">
         <v>5.0599999999999996</v>
       </c>
       <c r="I689" s="6" t="s">
@@ -29492,7 +29498,7 @@
       <c r="G690" s="5" t="s">
         <v>2644</v>
       </c>
-      <c r="H690" s="10">
+      <c r="H690" s="8">
         <v>5.0599999999999996</v>
       </c>
       <c r="I690" s="6" t="s">
@@ -29521,7 +29527,7 @@
       <c r="G691" s="5" t="s">
         <v>2651</v>
       </c>
-      <c r="H691" s="10">
+      <c r="H691" s="8">
         <v>87.32</v>
       </c>
       <c r="I691" s="6" t="s">
@@ -29550,7 +29556,7 @@
       <c r="G692" s="5" t="s">
         <v>2657</v>
       </c>
-      <c r="H692" s="10">
+      <c r="H692" s="8">
         <v>2801.86</v>
       </c>
       <c r="I692" s="6" t="s">
@@ -29579,7 +29585,7 @@
       <c r="G693" s="5" t="s">
         <v>2350</v>
       </c>
-      <c r="H693" s="10">
+      <c r="H693" s="8">
         <v>3673.5</v>
       </c>
       <c r="I693" s="6" t="s">
@@ -29608,7 +29614,7 @@
       <c r="G694" s="5" t="s">
         <v>2583</v>
       </c>
-      <c r="H694" s="10">
+      <c r="H694" s="8">
         <v>37.08</v>
       </c>
       <c r="I694" s="6" t="s">
@@ -29635,7 +29641,7 @@
       <c r="G695" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="H695" s="10">
+      <c r="H695" s="8">
         <v>35.49</v>
       </c>
       <c r="I695" s="6" t="s">
@@ -29662,7 +29668,7 @@
       <c r="G696" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="H696" s="10">
+      <c r="H696" s="8">
         <v>33.29</v>
       </c>
       <c r="I696" s="6" t="s">
@@ -29691,7 +29697,7 @@
       <c r="G697" s="5" t="s">
         <v>2681</v>
       </c>
-      <c r="H697" s="10">
+      <c r="H697" s="8">
         <v>66.55</v>
       </c>
       <c r="I697" s="6" t="s">
@@ -29720,7 +29726,7 @@
       <c r="G698" s="5" t="s">
         <v>2681</v>
       </c>
-      <c r="H698" s="10">
+      <c r="H698" s="8">
         <v>66.55</v>
       </c>
       <c r="I698" s="6" t="s">
@@ -29747,7 +29753,7 @@
       <c r="G699" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="H699" s="10">
+      <c r="H699" s="8">
         <v>34.44</v>
       </c>
       <c r="I699" s="6" t="s">
@@ -29774,7 +29780,7 @@
       <c r="G700" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="H700" s="10">
+      <c r="H700" s="8">
         <v>4.5199999999999996</v>
       </c>
       <c r="I700" s="6" t="s">
@@ -29803,7 +29809,7 @@
       <c r="G701" s="5" t="s">
         <v>2697</v>
       </c>
-      <c r="H701" s="10">
+      <c r="H701" s="8">
         <v>41.33</v>
       </c>
       <c r="I701" s="6" t="s">
@@ -29830,7 +29836,7 @@
       <c r="G702" s="5" t="s">
         <v>2701</v>
       </c>
-      <c r="H702" s="10">
+      <c r="H702" s="8">
         <v>135</v>
       </c>
       <c r="I702" s="6" t="s">
@@ -29857,7 +29863,7 @@
       <c r="G703" s="5" t="s">
         <v>2706</v>
       </c>
-      <c r="H703" s="10">
+      <c r="H703" s="8">
         <v>69.599999999999994</v>
       </c>
       <c r="I703" s="6" t="s">
@@ -29886,7 +29892,7 @@
       <c r="G704" s="5" t="s">
         <v>2712</v>
       </c>
-      <c r="H704" s="10">
+      <c r="H704" s="8">
         <v>89</v>
       </c>
       <c r="I704" s="6" t="s">
@@ -29915,7 +29921,7 @@
       <c r="G705" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="H705" s="10">
+      <c r="H705" s="8">
         <v>14.79</v>
       </c>
       <c r="I705" s="6" t="s">
@@ -29942,7 +29948,7 @@
       <c r="G706" s="5" t="s">
         <v>2721</v>
       </c>
-      <c r="H706" s="10">
+      <c r="H706" s="8">
         <v>28.09</v>
       </c>
       <c r="I706" s="6" t="s">
@@ -29969,7 +29975,7 @@
       <c r="G707" s="5" t="s">
         <v>2726</v>
       </c>
-      <c r="H707" s="10">
+      <c r="H707" s="8">
         <v>43.52</v>
       </c>
       <c r="I707" s="6" t="s">
@@ -29996,7 +30002,7 @@
       <c r="G708" s="5" t="s">
         <v>2726</v>
       </c>
-      <c r="H708" s="10">
+      <c r="H708" s="8">
         <v>43.52</v>
       </c>
       <c r="I708" s="6" t="s">
@@ -30025,7 +30031,7 @@
       <c r="G709" s="5" t="s">
         <v>2732</v>
       </c>
-      <c r="H709" s="10">
+      <c r="H709" s="8">
         <v>50.32</v>
       </c>
       <c r="I709" s="6" t="s">
@@ -30054,7 +30060,7 @@
       <c r="G710" s="5" t="s">
         <v>2739</v>
       </c>
-      <c r="H710" s="10">
+      <c r="H710" s="8">
         <v>139.35</v>
       </c>
       <c r="I710" s="6" t="s">
@@ -30083,7 +30089,7 @@
       <c r="G711" s="5" t="s">
         <v>2745</v>
       </c>
-      <c r="H711" s="10">
+      <c r="H711" s="8">
         <v>20.18</v>
       </c>
       <c r="I711" s="6" t="s">
@@ -30112,7 +30118,7 @@
       <c r="G712" s="5" t="s">
         <v>2745</v>
       </c>
-      <c r="H712" s="10">
+      <c r="H712" s="8">
         <v>20.18</v>
       </c>
       <c r="I712" s="6" t="s">
@@ -30139,7 +30145,7 @@
       <c r="G713" s="5" t="s">
         <v>2751</v>
       </c>
-      <c r="H713" s="10">
+      <c r="H713" s="8">
         <v>33.19</v>
       </c>
       <c r="I713" s="6" t="s">
@@ -30166,7 +30172,7 @@
       <c r="G714" s="5" t="s">
         <v>2751</v>
       </c>
-      <c r="H714" s="10">
+      <c r="H714" s="8">
         <v>33.19</v>
       </c>
       <c r="I714" s="6" t="s">
@@ -30193,7 +30199,7 @@
       <c r="G715" s="5" t="s">
         <v>2756</v>
       </c>
-      <c r="H715" s="10">
+      <c r="H715" s="8">
         <v>47.1</v>
       </c>
       <c r="I715" s="6" t="s">
@@ -30220,7 +30226,7 @@
       <c r="G716" s="5" t="s">
         <v>2761</v>
       </c>
-      <c r="H716" s="10">
+      <c r="H716" s="8">
         <v>109.6</v>
       </c>
       <c r="I716" s="6" t="s">
@@ -30247,7 +30253,7 @@
       <c r="G717" s="5" t="s">
         <v>2766</v>
       </c>
-      <c r="H717" s="10">
+      <c r="H717" s="8">
         <v>1.22</v>
       </c>
       <c r="I717" s="6" t="s">
@@ -30274,7 +30280,7 @@
       <c r="G718" s="5" t="s">
         <v>1187</v>
       </c>
-      <c r="H718" s="10">
+      <c r="H718" s="8">
         <v>15.12</v>
       </c>
       <c r="I718" s="6" t="s">
@@ -30301,7 +30307,7 @@
       <c r="G719" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="H719" s="10">
+      <c r="H719" s="8">
         <v>65.83</v>
       </c>
       <c r="I719" s="6" t="s">
@@ -30328,7 +30334,7 @@
       <c r="G720" s="5" t="s">
         <v>2779</v>
       </c>
-      <c r="H720" s="10">
+      <c r="H720" s="8">
         <v>37.950000000000003</v>
       </c>
       <c r="I720" s="6" t="s">
@@ -30355,7 +30361,7 @@
       <c r="G721" s="5" t="s">
         <v>2779</v>
       </c>
-      <c r="H721" s="10">
+      <c r="H721" s="8">
         <v>37.950000000000003</v>
       </c>
       <c r="I721" s="6" t="s">
@@ -30382,7 +30388,7 @@
       <c r="G722" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H722" s="10">
+      <c r="H722" s="8">
         <v>67.260000000000005</v>
       </c>
       <c r="I722" s="6" t="s">
@@ -30409,7 +30415,7 @@
       <c r="G723" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H723" s="10">
+      <c r="H723" s="8">
         <v>67.260000000000005</v>
       </c>
       <c r="I723" s="6" t="s">
@@ -30436,7 +30442,7 @@
       <c r="G724" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H724" s="10">
+      <c r="H724" s="8">
         <v>33.96</v>
       </c>
       <c r="I724" s="6" t="s">
@@ -30463,7 +30469,7 @@
       <c r="G725" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H725" s="10">
+      <c r="H725" s="8">
         <v>33.96</v>
       </c>
       <c r="I725" s="6" t="s">
@@ -30490,7 +30496,7 @@
       <c r="G726" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="H726" s="10">
+      <c r="H726" s="8">
         <v>44.42</v>
       </c>
       <c r="I726" s="6" t="s">
@@ -30517,7 +30523,7 @@
       <c r="G727" s="5" t="s">
         <v>2794</v>
       </c>
-      <c r="H727" s="10">
+      <c r="H727" s="8">
         <v>14.88</v>
       </c>
       <c r="I727" s="6" t="s">
@@ -30544,7 +30550,7 @@
       <c r="G728" s="5" t="s">
         <v>2799</v>
       </c>
-      <c r="H728" s="10">
+      <c r="H728" s="8">
         <v>19.079999999999998</v>
       </c>
       <c r="I728" s="6" t="s">
@@ -30571,7 +30577,7 @@
       <c r="G729" s="5" t="s">
         <v>2799</v>
       </c>
-      <c r="H729" s="10">
+      <c r="H729" s="8">
         <v>19.079999999999998</v>
       </c>
       <c r="I729" s="6" t="s">
@@ -30598,7 +30604,7 @@
       <c r="G730" s="5" t="s">
         <v>2804</v>
       </c>
-      <c r="H730" s="10">
+      <c r="H730" s="8">
         <v>8.3699999999999992</v>
       </c>
       <c r="I730" s="6" t="s">
@@ -30625,7 +30631,7 @@
       <c r="G731" s="5" t="s">
         <v>2804</v>
       </c>
-      <c r="H731" s="10">
+      <c r="H731" s="8">
         <v>8.3699999999999992</v>
       </c>
       <c r="I731" s="6" t="s">
@@ -30652,7 +30658,7 @@
       <c r="G732" s="5" t="s">
         <v>2810</v>
       </c>
-      <c r="H732" s="10">
+      <c r="H732" s="8">
         <v>23.3</v>
       </c>
       <c r="I732" s="6" t="s">
@@ -30679,7 +30685,7 @@
       <c r="G733" s="5" t="s">
         <v>2810</v>
       </c>
-      <c r="H733" s="10">
+      <c r="H733" s="8">
         <v>23.3</v>
       </c>
       <c r="I733" s="6" t="s">
@@ -30706,7 +30712,7 @@
       <c r="G734" s="5" t="s">
         <v>2815</v>
       </c>
-      <c r="H734" s="10">
+      <c r="H734" s="8">
         <v>114.24</v>
       </c>
       <c r="I734" s="6" t="s">
@@ -30733,7 +30739,7 @@
       <c r="G735" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H735" s="10">
+      <c r="H735" s="8">
         <v>72.209999999999994</v>
       </c>
       <c r="I735" s="6" t="s">
@@ -30760,7 +30766,7 @@
       <c r="G736" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H736" s="10">
+      <c r="H736" s="8">
         <v>72.209999999999994</v>
       </c>
       <c r="I736" s="6" t="s">
@@ -30787,7 +30793,7 @@
       <c r="G737" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H737" s="10">
+      <c r="H737" s="8">
         <v>46.44</v>
       </c>
       <c r="I737" s="6" t="s">
@@ -30814,7 +30820,7 @@
       <c r="G738" s="5" t="s">
         <v>2829</v>
       </c>
-      <c r="H738" s="10">
+      <c r="H738" s="8">
         <v>23.72</v>
       </c>
       <c r="I738" s="6" t="s">
@@ -30841,7 +30847,7 @@
       <c r="G739" s="5" t="s">
         <v>2829</v>
       </c>
-      <c r="H739" s="10">
+      <c r="H739" s="8">
         <v>23.72</v>
       </c>
       <c r="I739" s="6" t="s">
@@ -30868,7 +30874,7 @@
       <c r="G740" s="5" t="s">
         <v>2834</v>
       </c>
-      <c r="H740" s="10">
+      <c r="H740" s="8">
         <v>35</v>
       </c>
       <c r="I740" s="6" t="s">
@@ -30895,7 +30901,7 @@
       <c r="G741" s="5" t="s">
         <v>2834</v>
       </c>
-      <c r="H741" s="10">
+      <c r="H741" s="8">
         <v>35</v>
       </c>
       <c r="I741" s="6" t="s">
@@ -30922,7 +30928,7 @@
       <c r="G742" s="5" t="s">
         <v>2839</v>
       </c>
-      <c r="H742" s="10">
+      <c r="H742" s="8">
         <v>71.03</v>
       </c>
       <c r="I742" s="6" t="s">
@@ -30949,7 +30955,7 @@
       <c r="G743" s="5" t="s">
         <v>2839</v>
       </c>
-      <c r="H743" s="10">
+      <c r="H743" s="8">
         <v>71.03</v>
       </c>
       <c r="I743" s="6" t="s">
@@ -30976,7 +30982,7 @@
       <c r="G744" s="5" t="s">
         <v>2844</v>
       </c>
-      <c r="H744" s="10">
+      <c r="H744" s="8">
         <v>40.32</v>
       </c>
       <c r="I744" s="6" t="s">
@@ -31003,7 +31009,7 @@
       <c r="G745" s="5" t="s">
         <v>2844</v>
       </c>
-      <c r="H745" s="10">
+      <c r="H745" s="8">
         <v>40.32</v>
       </c>
       <c r="I745" s="6" t="s">
@@ -31030,7 +31036,7 @@
       <c r="G746" s="5" t="s">
         <v>2850</v>
       </c>
-      <c r="H746" s="10">
+      <c r="H746" s="8">
         <v>93.5</v>
       </c>
       <c r="I746" s="6" t="s">
@@ -31057,7 +31063,7 @@
       <c r="G747" s="5" t="s">
         <v>2850</v>
       </c>
-      <c r="H747" s="10">
+      <c r="H747" s="8">
         <v>93.5</v>
       </c>
       <c r="I747" s="6" t="s">
@@ -31084,7 +31090,7 @@
       <c r="G748" s="5" t="s">
         <v>2855</v>
       </c>
-      <c r="H748" s="10">
+      <c r="H748" s="8">
         <v>45.38</v>
       </c>
       <c r="I748" s="6" t="s">
@@ -31111,7 +31117,7 @@
       <c r="G749" s="5" t="s">
         <v>2855</v>
       </c>
-      <c r="H749" s="10">
+      <c r="H749" s="8">
         <v>45.38</v>
       </c>
       <c r="I749" s="6" t="s">
@@ -31138,7 +31144,7 @@
       <c r="G750" s="5" t="s">
         <v>2860</v>
       </c>
-      <c r="H750" s="10">
+      <c r="H750" s="8">
         <v>43.3</v>
       </c>
       <c r="I750" s="6" t="s">
@@ -31165,7 +31171,7 @@
       <c r="G751" s="5" t="s">
         <v>2860</v>
       </c>
-      <c r="H751" s="10">
+      <c r="H751" s="8">
         <v>43.3</v>
       </c>
       <c r="I751" s="6" t="s">
@@ -31192,7 +31198,7 @@
       <c r="G752" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H752" s="10">
+      <c r="H752" s="8">
         <v>29.95</v>
       </c>
       <c r="I752" s="6" t="s">
@@ -31219,7 +31225,7 @@
       <c r="G753" s="5" t="s">
         <v>2868</v>
       </c>
-      <c r="H753" s="10">
+      <c r="H753" s="8">
         <v>68</v>
       </c>
       <c r="I753" s="6" t="s">
@@ -31246,7 +31252,7 @@
       <c r="G754" s="5" t="s">
         <v>2810</v>
       </c>
-      <c r="H754" s="10">
+      <c r="H754" s="8">
         <v>25.48</v>
       </c>
       <c r="I754" s="6" t="s">
@@ -31273,7 +31279,7 @@
       <c r="G755" s="5" t="s">
         <v>2810</v>
       </c>
-      <c r="H755" s="10">
+      <c r="H755" s="8">
         <v>25.48</v>
       </c>
       <c r="I755" s="6" t="s">
@@ -31300,7 +31306,7 @@
       <c r="G756" s="5" t="s">
         <v>2878</v>
       </c>
-      <c r="H756" s="10">
+      <c r="H756" s="8">
         <v>79.599999999999994</v>
       </c>
       <c r="I756" s="6" t="s">
@@ -31327,7 +31333,7 @@
       <c r="G757" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H757" s="10">
+      <c r="H757" s="8">
         <v>50</v>
       </c>
       <c r="I757" s="6" t="s">
@@ -31354,7 +31360,7 @@
       <c r="G758" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H758" s="10">
+      <c r="H758" s="8">
         <v>50</v>
       </c>
       <c r="I758" s="6" t="s">
@@ -31381,7 +31387,7 @@
       <c r="G759" s="5" t="s">
         <v>2887</v>
       </c>
-      <c r="H759" s="10">
+      <c r="H759" s="8">
         <v>115.67</v>
       </c>
       <c r="I759" s="6" t="s">
@@ -31408,7 +31414,7 @@
       <c r="G760" s="5" t="s">
         <v>2887</v>
       </c>
-      <c r="H760" s="10">
+      <c r="H760" s="8">
         <v>115.67</v>
       </c>
       <c r="I760" s="6" t="s">
@@ -31435,7 +31441,7 @@
       <c r="G761" s="5" t="s">
         <v>2892</v>
       </c>
-      <c r="H761" s="10">
+      <c r="H761" s="8">
         <v>108</v>
       </c>
       <c r="I761" s="6" t="s">
@@ -31462,7 +31468,7 @@
       <c r="G762" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H762" s="10">
+      <c r="H762" s="8">
         <v>26.38</v>
       </c>
       <c r="I762" s="6" t="s">
@@ -31489,7 +31495,7 @@
       <c r="G763" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H763" s="10">
+      <c r="H763" s="8">
         <v>26.38</v>
       </c>
       <c r="I763" s="6" t="s">
@@ -31516,7 +31522,7 @@
       <c r="G764" s="5" t="s">
         <v>2901</v>
       </c>
-      <c r="H764" s="10">
+      <c r="H764" s="8">
         <v>37.4</v>
       </c>
       <c r="I764" s="6" t="s">
@@ -31543,7 +31549,7 @@
       <c r="G765" s="5" t="s">
         <v>2901</v>
       </c>
-      <c r="H765" s="10">
+      <c r="H765" s="8">
         <v>37.4</v>
       </c>
       <c r="I765" s="6" t="s">
@@ -31570,7 +31576,7 @@
       <c r="G766" s="5" t="s">
         <v>2906</v>
       </c>
-      <c r="H766" s="10">
+      <c r="H766" s="8">
         <v>38.520000000000003</v>
       </c>
       <c r="I766" s="6" t="s">
@@ -31597,7 +31603,7 @@
       <c r="G767" s="5" t="s">
         <v>2906</v>
       </c>
-      <c r="H767" s="10">
+      <c r="H767" s="8">
         <v>38.520000000000003</v>
       </c>
       <c r="I767" s="6" t="s">
@@ -31624,7 +31630,7 @@
       <c r="G768" s="5" t="s">
         <v>2911</v>
       </c>
-      <c r="H768" s="10">
+      <c r="H768" s="8">
         <v>29.51</v>
       </c>
       <c r="I768" s="6" t="s">
@@ -31651,7 +31657,7 @@
       <c r="G769" s="5" t="s">
         <v>2911</v>
       </c>
-      <c r="H769" s="10">
+      <c r="H769" s="8">
         <v>29.51</v>
       </c>
       <c r="I769" s="6" t="s">
@@ -31678,7 +31684,7 @@
       <c r="G770" s="5" t="s">
         <v>2917</v>
       </c>
-      <c r="H770" s="10">
+      <c r="H770" s="8">
         <v>24.8</v>
       </c>
       <c r="I770" s="6" t="s">
@@ -31705,7 +31711,7 @@
       <c r="G771" s="5" t="s">
         <v>2917</v>
       </c>
-      <c r="H771" s="10">
+      <c r="H771" s="8">
         <v>24.8</v>
       </c>
       <c r="I771" s="6" t="s">
@@ -31732,7 +31738,7 @@
       <c r="G772" s="5" t="s">
         <v>2922</v>
       </c>
-      <c r="H772" s="10">
+      <c r="H772" s="8">
         <v>22.18</v>
       </c>
       <c r="I772" s="6" t="s">
@@ -31759,7 +31765,7 @@
       <c r="G773" s="5" t="s">
         <v>2922</v>
       </c>
-      <c r="H773" s="10">
+      <c r="H773" s="8">
         <v>22.18</v>
       </c>
       <c r="I773" s="6" t="s">
@@ -31786,7 +31792,7 @@
       <c r="G774" s="5" t="s">
         <v>2928</v>
       </c>
-      <c r="H774" s="10">
+      <c r="H774" s="8">
         <v>25.98</v>
       </c>
       <c r="I774" s="6" t="s">
@@ -31813,7 +31819,7 @@
       <c r="G775" s="5" t="s">
         <v>2928</v>
       </c>
-      <c r="H775" s="10">
+      <c r="H775" s="8">
         <v>25.98</v>
       </c>
       <c r="I775" s="6" t="s">
@@ -31840,7 +31846,7 @@
       <c r="G776" s="5" t="s">
         <v>2933</v>
       </c>
-      <c r="H776" s="10">
+      <c r="H776" s="8">
         <v>34.270000000000003</v>
       </c>
       <c r="I776" s="6" t="s">
@@ -31867,7 +31873,7 @@
       <c r="G777" s="5" t="s">
         <v>2933</v>
       </c>
-      <c r="H777" s="10">
+      <c r="H777" s="8">
         <v>34.270000000000003</v>
       </c>
       <c r="I777" s="6" t="s">
@@ -31896,7 +31902,7 @@
       <c r="G778" s="5" t="s">
         <v>2940</v>
       </c>
-      <c r="H778" s="10">
+      <c r="H778" s="8">
         <v>21.77</v>
       </c>
       <c r="I778" s="6" t="s">
@@ -31925,7 +31931,7 @@
       <c r="G779" s="5" t="s">
         <v>2940</v>
       </c>
-      <c r="H779" s="10">
+      <c r="H779" s="8">
         <v>21.77</v>
       </c>
       <c r="I779" s="6" t="s">
@@ -31952,7 +31958,7 @@
       <c r="G780" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H780" s="10">
+      <c r="H780" s="8">
         <v>46.6</v>
       </c>
       <c r="I780" s="6" t="s">
@@ -31979,7 +31985,7 @@
       <c r="G781" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H781" s="10">
+      <c r="H781" s="8">
         <v>46.6</v>
       </c>
       <c r="I781" s="6" t="s">
@@ -32006,7 +32012,7 @@
       <c r="G782" s="5" t="s">
         <v>2949</v>
       </c>
-      <c r="H782" s="10">
+      <c r="H782" s="8">
         <v>30.71</v>
       </c>
       <c r="I782" s="6" t="s">
@@ -32033,7 +32039,7 @@
       <c r="G783" s="5" t="s">
         <v>2949</v>
       </c>
-      <c r="H783" s="10">
+      <c r="H783" s="8">
         <v>30.71</v>
       </c>
       <c r="I783" s="6" t="s">
@@ -32058,7 +32064,7 @@
       <c r="G784" s="5" t="s">
         <v>2954</v>
       </c>
-      <c r="H784" s="10">
+      <c r="H784" s="8">
         <v>12</v>
       </c>
       <c r="I784" s="6" t="s">
@@ -32085,7 +32091,7 @@
       <c r="G785" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H785" s="10">
+      <c r="H785" s="8">
         <v>32.72</v>
       </c>
       <c r="I785" s="6" t="s">
@@ -32112,7 +32118,7 @@
       <c r="G786" s="5" t="s">
         <v>2825</v>
       </c>
-      <c r="H786" s="10">
+      <c r="H786" s="8">
         <v>32.72</v>
       </c>
       <c r="I786" s="6" t="s">
@@ -32139,7 +32145,7 @@
       <c r="G787" s="5" t="s">
         <v>2960</v>
       </c>
-      <c r="H787" s="10">
+      <c r="H787" s="8">
         <v>161.87</v>
       </c>
       <c r="I787" s="6" t="s">
@@ -32166,7 +32172,7 @@
       <c r="G788" s="5" t="s">
         <v>2960</v>
       </c>
-      <c r="H788" s="10">
+      <c r="H788" s="8">
         <v>161.87</v>
       </c>
       <c r="I788" s="6" t="s">
@@ -32193,7 +32199,7 @@
       <c r="G789" s="5" t="s">
         <v>2965</v>
       </c>
-      <c r="H789" s="10">
+      <c r="H789" s="8">
         <v>20.92</v>
       </c>
       <c r="I789" s="6" t="s">
@@ -32222,7 +32228,7 @@
       <c r="G790" s="5" t="s">
         <v>2971</v>
       </c>
-      <c r="H790" s="10">
+      <c r="H790" s="8">
         <v>11.36</v>
       </c>
       <c r="I790" s="6" t="s">
@@ -32251,7 +32257,7 @@
       <c r="G791" s="5" t="s">
         <v>2971</v>
       </c>
-      <c r="H791" s="10">
+      <c r="H791" s="8">
         <v>11.36</v>
       </c>
       <c r="I791" s="6" t="s">
@@ -32280,7 +32286,7 @@
       <c r="G792" s="5" t="s">
         <v>2978</v>
       </c>
-      <c r="H792" s="10">
+      <c r="H792" s="8">
         <v>19.7</v>
       </c>
       <c r="I792" s="6" t="s">
@@ -32309,7 +32315,7 @@
       <c r="G793" s="5" t="s">
         <v>2978</v>
       </c>
-      <c r="H793" s="10">
+      <c r="H793" s="8">
         <v>19.7</v>
       </c>
       <c r="I793" s="6" t="s">
@@ -32336,7 +32342,7 @@
       <c r="G794" s="5" t="s">
         <v>2985</v>
       </c>
-      <c r="H794" s="10">
+      <c r="H794" s="8">
         <v>39.590000000000003</v>
       </c>
       <c r="I794" s="6" t="s">
@@ -32363,7 +32369,7 @@
       <c r="G795" s="5" t="s">
         <v>2990</v>
       </c>
-      <c r="H795" s="10">
+      <c r="H795" s="8">
         <v>27.05</v>
       </c>
       <c r="I795" s="6" t="s">
@@ -32390,7 +32396,7 @@
       <c r="G796" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H796" s="10">
+      <c r="H796" s="8">
         <v>21.41</v>
       </c>
       <c r="I796" s="6" t="s">
@@ -32417,7 +32423,7 @@
       <c r="G797" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H797" s="10">
+      <c r="H797" s="8">
         <v>21.41</v>
       </c>
       <c r="I797" s="6" t="s">
@@ -32444,7 +32450,7 @@
       <c r="G798" s="5" t="s">
         <v>2999</v>
       </c>
-      <c r="H798" s="10">
+      <c r="H798" s="8">
         <v>50.52</v>
       </c>
       <c r="I798" s="6" t="s">
@@ -32471,7 +32477,7 @@
       <c r="G799" s="5" t="s">
         <v>2999</v>
       </c>
-      <c r="H799" s="10">
+      <c r="H799" s="8">
         <v>50.52</v>
       </c>
       <c r="I799" s="6" t="s">
@@ -32498,7 +32504,7 @@
       <c r="G800" s="5" t="s">
         <v>2985</v>
       </c>
-      <c r="H800" s="10">
+      <c r="H800" s="8">
         <v>49.65</v>
       </c>
       <c r="I800" s="6" t="s">
@@ -32525,7 +32531,7 @@
       <c r="G801" s="5" t="s">
         <v>2985</v>
       </c>
-      <c r="H801" s="10">
+      <c r="H801" s="8">
         <v>49.65</v>
       </c>
       <c r="I801" s="6" t="s">
@@ -32552,7 +32558,7 @@
       <c r="G802" s="5" t="s">
         <v>3007</v>
       </c>
-      <c r="H802" s="10">
+      <c r="H802" s="8">
         <v>36.96</v>
       </c>
       <c r="I802" s="6" t="s">
@@ -32579,7 +32585,7 @@
       <c r="G803" s="5" t="s">
         <v>2990</v>
       </c>
-      <c r="H803" s="10">
+      <c r="H803" s="8">
         <v>20.22</v>
       </c>
       <c r="I803" s="6" t="s">
@@ -32606,7 +32612,7 @@
       <c r="G804" s="5" t="s">
         <v>2922</v>
       </c>
-      <c r="H804" s="10">
+      <c r="H804" s="8">
         <v>31.29</v>
       </c>
       <c r="I804" s="6" t="s">
@@ -32633,7 +32639,7 @@
       <c r="G805" s="5" t="s">
         <v>2922</v>
       </c>
-      <c r="H805" s="10">
+      <c r="H805" s="8">
         <v>31.29</v>
       </c>
       <c r="I805" s="6" t="s">
@@ -32662,7 +32668,7 @@
       <c r="G806" s="5" t="s">
         <v>3020</v>
       </c>
-      <c r="H806" s="10">
+      <c r="H806" s="8">
         <v>49.54</v>
       </c>
       <c r="I806" s="6" t="s">
@@ -32689,7 +32695,7 @@
       <c r="G807" s="5" t="s">
         <v>3025</v>
       </c>
-      <c r="H807" s="10">
+      <c r="H807" s="8">
         <v>33.590000000000003</v>
       </c>
       <c r="I807" s="6" t="s">
@@ -32716,7 +32722,7 @@
       <c r="G808" s="5" t="s">
         <v>3025</v>
       </c>
-      <c r="H808" s="10">
+      <c r="H808" s="8">
         <v>33.590000000000003</v>
       </c>
       <c r="I808" s="6" t="s">
@@ -32743,7 +32749,7 @@
       <c r="G809" s="5" t="s">
         <v>3030</v>
       </c>
-      <c r="H809" s="10">
+      <c r="H809" s="8">
         <v>36.549999999999997</v>
       </c>
       <c r="I809" s="6" t="s">
@@ -32770,7 +32776,7 @@
       <c r="G810" s="5" t="s">
         <v>3035</v>
       </c>
-      <c r="H810" s="10">
+      <c r="H810" s="8">
         <v>30.01</v>
       </c>
       <c r="I810" s="6" t="s">
@@ -32797,7 +32803,7 @@
       <c r="G811" s="5" t="s">
         <v>3035</v>
       </c>
-      <c r="H811" s="10">
+      <c r="H811" s="8">
         <v>30.01</v>
       </c>
       <c r="I811" s="6" t="s">
@@ -32824,7 +32830,7 @@
       <c r="G812" s="5" t="s">
         <v>3040</v>
       </c>
-      <c r="H812" s="10">
+      <c r="H812" s="8">
         <v>55.18</v>
       </c>
       <c r="I812" s="6" t="s">
@@ -32851,7 +32857,7 @@
       <c r="G813" s="5" t="s">
         <v>3044</v>
       </c>
-      <c r="H813" s="10">
+      <c r="H813" s="8">
         <v>41.75</v>
       </c>
       <c r="I813" s="6" t="s">
@@ -32878,7 +32884,7 @@
       <c r="G814" s="5" t="s">
         <v>3044</v>
       </c>
-      <c r="H814" s="10">
+      <c r="H814" s="8">
         <v>41.75</v>
       </c>
       <c r="I814" s="6" t="s">
@@ -32905,7 +32911,7 @@
       <c r="G815" s="5" t="s">
         <v>3050</v>
       </c>
-      <c r="H815" s="10">
+      <c r="H815" s="8">
         <v>34.24</v>
       </c>
       <c r="I815" s="6" t="s">
@@ -32932,7 +32938,7 @@
       <c r="G816" s="5" t="s">
         <v>3050</v>
       </c>
-      <c r="H816" s="10">
+      <c r="H816" s="8">
         <v>34.24</v>
       </c>
       <c r="I816" s="6" t="s">
@@ -32959,7 +32965,7 @@
       <c r="G817" s="5" t="s">
         <v>3055</v>
       </c>
-      <c r="H817" s="10">
+      <c r="H817" s="8">
         <v>43.42</v>
       </c>
       <c r="I817" s="6" t="s">
@@ -32986,7 +32992,7 @@
       <c r="G818" s="5" t="s">
         <v>3060</v>
       </c>
-      <c r="H818" s="10">
+      <c r="H818" s="8">
         <v>66.959999999999994</v>
       </c>
       <c r="I818" s="6" t="s">
@@ -33013,7 +33019,7 @@
       <c r="G819" s="5" t="s">
         <v>3060</v>
       </c>
-      <c r="H819" s="10">
+      <c r="H819" s="8">
         <v>66.959999999999994</v>
       </c>
       <c r="I819" s="6" t="s">
@@ -33040,7 +33046,7 @@
       <c r="G820" s="5" t="s">
         <v>3065</v>
       </c>
-      <c r="H820" s="10">
+      <c r="H820" s="8">
         <v>44.6</v>
       </c>
       <c r="I820" s="6" t="s">
@@ -33067,7 +33073,7 @@
       <c r="G821" s="5" t="s">
         <v>3065</v>
       </c>
-      <c r="H821" s="10">
+      <c r="H821" s="8">
         <v>44.6</v>
       </c>
       <c r="I821" s="6" t="s">
@@ -33094,7 +33100,7 @@
       <c r="G822" s="5" t="s">
         <v>3070</v>
       </c>
-      <c r="H822" s="10">
+      <c r="H822" s="8">
         <v>17.260000000000002</v>
       </c>
       <c r="I822" s="6" t="s">
@@ -33121,7 +33127,7 @@
       <c r="G823" s="5" t="s">
         <v>2475</v>
       </c>
-      <c r="H823" s="10">
+      <c r="H823" s="8">
         <v>16.98</v>
       </c>
       <c r="I823" s="6" t="s">
@@ -33148,7 +33154,7 @@
       <c r="G824" s="5" t="s">
         <v>2475</v>
       </c>
-      <c r="H824" s="10">
+      <c r="H824" s="8">
         <v>16.98</v>
       </c>
       <c r="I824" s="6" t="s">
@@ -33177,7 +33183,7 @@
       <c r="G825" s="5" t="s">
         <v>3081</v>
       </c>
-      <c r="H825" s="10">
+      <c r="H825" s="8">
         <v>44.09</v>
       </c>
       <c r="I825" s="6" t="s">
@@ -33204,7 +33210,7 @@
       <c r="G826" s="5" t="s">
         <v>3085</v>
       </c>
-      <c r="H826" s="10">
+      <c r="H826" s="8">
         <v>265.61</v>
       </c>
       <c r="I826" s="6" t="s">
@@ -33231,7 +33237,7 @@
       <c r="G827" s="5" t="s">
         <v>3089</v>
       </c>
-      <c r="H827" s="10">
+      <c r="H827" s="8">
         <v>83</v>
       </c>
       <c r="I827" s="6" t="s">
@@ -33258,7 +33264,7 @@
       <c r="G828" s="5" t="s">
         <v>3095</v>
       </c>
-      <c r="H828" s="10">
+      <c r="H828" s="8">
         <v>20.45</v>
       </c>
       <c r="I828" s="6" t="s">
@@ -33285,7 +33291,7 @@
       <c r="G829" s="5" t="s">
         <v>3095</v>
       </c>
-      <c r="H829" s="10">
+      <c r="H829" s="8">
         <v>20.45</v>
       </c>
       <c r="I829" s="6" t="s">
@@ -33312,7 +33318,7 @@
       <c r="G830" s="5" t="s">
         <v>3101</v>
       </c>
-      <c r="H830" s="10">
+      <c r="H830" s="8">
         <v>13.79</v>
       </c>
       <c r="I830" s="6" t="s">
@@ -33339,7 +33345,7 @@
       <c r="G831" s="5" t="s">
         <v>3101</v>
       </c>
-      <c r="H831" s="10">
+      <c r="H831" s="8">
         <v>13.79</v>
       </c>
       <c r="I831" s="6" t="s">
@@ -33366,7 +33372,7 @@
       <c r="G832" s="5" t="s">
         <v>3107</v>
       </c>
-      <c r="H832" s="10">
+      <c r="H832" s="8">
         <v>74.88</v>
       </c>
       <c r="I832" s="6" t="s">
@@ -33393,7 +33399,7 @@
       <c r="G833" s="5" t="s">
         <v>3112</v>
       </c>
-      <c r="H833" s="10">
+      <c r="H833" s="8">
         <v>155.5</v>
       </c>
       <c r="I833" s="6" t="s">
@@ -33420,7 +33426,7 @@
       <c r="G834" s="5" t="s">
         <v>3116</v>
       </c>
-      <c r="H834" s="10">
+      <c r="H834" s="8">
         <v>115.98</v>
       </c>
       <c r="I834" s="6" t="s">
@@ -33447,7 +33453,7 @@
       <c r="G835" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="H835" s="10">
+      <c r="H835" s="8">
         <v>66.59</v>
       </c>
       <c r="I835" s="6" t="s">
@@ -33474,7 +33480,7 @@
       <c r="G836" s="5" t="s">
         <v>3125</v>
       </c>
-      <c r="H836" s="10">
+      <c r="H836" s="8">
         <v>38.04</v>
       </c>
       <c r="I836" s="6" t="s">
@@ -33501,7 +33507,7 @@
       <c r="G837" s="5" t="s">
         <v>3130</v>
       </c>
-      <c r="H837" s="10">
+      <c r="H837" s="8">
         <v>39.82</v>
       </c>
       <c r="I837" s="6" t="s">
@@ -33528,7 +33534,7 @@
       <c r="G838" s="5" t="s">
         <v>3135</v>
       </c>
-      <c r="H838" s="10">
+      <c r="H838" s="8">
         <v>38.26</v>
       </c>
       <c r="I838" s="6" t="s">
@@ -33555,7 +33561,7 @@
       <c r="G839" s="5" t="s">
         <v>1973</v>
       </c>
-      <c r="H839" s="10">
+      <c r="H839" s="8">
         <v>66</v>
       </c>
       <c r="I839" s="6" t="s">
@@ -33582,7 +33588,7 @@
       <c r="G840" s="5" t="s">
         <v>3135</v>
       </c>
-      <c r="H840" s="10">
+      <c r="H840" s="8">
         <v>24.39</v>
       </c>
       <c r="I840" s="6" t="s">
@@ -33609,7 +33615,7 @@
       <c r="G841" s="5" t="s">
         <v>3148</v>
       </c>
-      <c r="H841" s="10">
+      <c r="H841" s="8">
         <v>27.45</v>
       </c>
       <c r="I841" s="6" t="s">
@@ -33636,7 +33642,7 @@
       <c r="G842" s="5" t="s">
         <v>3152</v>
       </c>
-      <c r="H842" s="10">
+      <c r="H842" s="8">
         <v>41.03</v>
       </c>
       <c r="I842" s="6" t="s">
@@ -33663,7 +33669,7 @@
       <c r="G843" s="5" t="s">
         <v>3152</v>
       </c>
-      <c r="H843" s="10">
+      <c r="H843" s="8">
         <v>41.03</v>
       </c>
       <c r="I843" s="6" t="s">
@@ -33690,7 +33696,7 @@
       <c r="G844" s="5" t="s">
         <v>3157</v>
       </c>
-      <c r="H844" s="10">
+      <c r="H844" s="8">
         <v>30.8</v>
       </c>
       <c r="I844" s="6" t="s">
@@ -33717,7 +33723,7 @@
       <c r="G845" s="5" t="s">
         <v>3157</v>
       </c>
-      <c r="H845" s="10">
+      <c r="H845" s="8">
         <v>30.8</v>
       </c>
       <c r="I845" s="6" t="s">
@@ -33744,7 +33750,7 @@
       <c r="G846" s="5" t="s">
         <v>3161</v>
       </c>
-      <c r="H846" s="10">
+      <c r="H846" s="8">
         <v>24</v>
       </c>
       <c r="I846" s="6" t="s">
@@ -33771,7 +33777,7 @@
       <c r="G847" s="5" t="s">
         <v>3166</v>
       </c>
-      <c r="H847" s="10">
+      <c r="H847" s="8">
         <v>38.85</v>
       </c>
       <c r="I847" s="6" t="s">
@@ -33798,7 +33804,7 @@
       <c r="G848" s="5" t="s">
         <v>3171</v>
       </c>
-      <c r="H848" s="10">
+      <c r="H848" s="8">
         <v>37.049999999999997</v>
       </c>
       <c r="I848" s="6" t="s">
@@ -33825,7 +33831,7 @@
       <c r="G849" s="5" t="s">
         <v>3171</v>
       </c>
-      <c r="H849" s="10">
+      <c r="H849" s="8">
         <v>37.049999999999997</v>
       </c>
       <c r="I849" s="6" t="s">
@@ -33852,7 +33858,7 @@
       <c r="G850" s="5" t="s">
         <v>3157</v>
       </c>
-      <c r="H850" s="10">
+      <c r="H850" s="8">
         <v>33.700000000000003</v>
       </c>
       <c r="I850" s="6" t="s">
@@ -33879,7 +33885,7 @@
       <c r="G851" s="5" t="s">
         <v>3157</v>
       </c>
-      <c r="H851" s="10">
+      <c r="H851" s="8">
         <v>33.700000000000003</v>
       </c>
       <c r="I851" s="6" t="s">
@@ -33906,7 +33912,7 @@
       <c r="G852" s="5" t="s">
         <v>3182</v>
       </c>
-      <c r="H852" s="10">
+      <c r="H852" s="8">
         <v>66.959999999999994</v>
       </c>
       <c r="I852" s="6" t="s">
@@ -33933,7 +33939,7 @@
       <c r="G853" s="5" t="s">
         <v>3182</v>
       </c>
-      <c r="H853" s="10">
+      <c r="H853" s="8">
         <v>66.959999999999994</v>
       </c>
       <c r="I853" s="6" t="s">
@@ -33960,7 +33966,7 @@
       <c r="G854" s="5" t="s">
         <v>3187</v>
       </c>
-      <c r="H854" s="10">
+      <c r="H854" s="8">
         <v>21.33</v>
       </c>
       <c r="I854" s="6" t="s">
@@ -33987,7 +33993,7 @@
       <c r="G855" s="5" t="s">
         <v>3187</v>
       </c>
-      <c r="H855" s="10">
+      <c r="H855" s="8">
         <v>21.33</v>
       </c>
       <c r="I855" s="6" t="s">
@@ -34014,7 +34020,7 @@
       <c r="G856" s="5" t="s">
         <v>3192</v>
       </c>
-      <c r="H856" s="10">
+      <c r="H856" s="8">
         <v>85.3</v>
       </c>
       <c r="I856" s="6" t="s">
